--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,6 +1689,4044 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122646865</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79766</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550706</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7245002</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122646878</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97194</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550829</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7245185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122646850</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>550760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7244829</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122646824</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550678</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7244623</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122646849</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550779</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7244796</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122647137</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91182</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550827</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7245136</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122646822</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96108</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550659</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7244555</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122646864</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550696</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7244978</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122647144</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550854</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7245180</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122646872</v>
+      </c>
+      <c r="B20" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550828</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7245091</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122646868</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550694</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7245016</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122646857</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74762</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550751</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7244916</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122647146</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57303</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550861</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7245193</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122646845</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550631</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7244710</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122646853</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550761</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7244876</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122646846</v>
+      </c>
+      <c r="B26" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550720</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7244779</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122646854</v>
+      </c>
+      <c r="B27" t="n">
+        <v>94641</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>550764</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7244897</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122646823</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550677</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7244586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122647138</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550832</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7245128</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122646855</v>
+      </c>
+      <c r="B30" t="n">
+        <v>94641</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550770</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7244875</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122646808</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550651</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7244779</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122646861</v>
+      </c>
+      <c r="B32" t="n">
+        <v>74741</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550710</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7244974</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122647136</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91124</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550831</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7245134</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122646873</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550828</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7245125</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122647145</v>
+      </c>
+      <c r="B35" t="n">
+        <v>88192</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>510</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550855</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7245196</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122646874</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74762</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550824</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7245149</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122646870</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74752</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>310</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550726</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7245050</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122646856</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550759</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7244890</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122647126</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91124</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>550801</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7244998</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122646869</v>
+      </c>
+      <c r="B40" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>550688</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7245034</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122646848</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91521</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550776</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7244797</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122646852</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91521</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>550744</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7244856</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122646871</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>550784</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7245041</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122646851</v>
+      </c>
+      <c r="B44" t="n">
+        <v>74757</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>550748</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7244855</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122646863</v>
+      </c>
+      <c r="B45" t="n">
+        <v>94653</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>550698</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7244980</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122646847</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>550746</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7244802</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122646866</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>550706</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7245009</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122646821</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74752</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>310</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>550670</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7244542</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646865</v>
+        <v>122647146</v>
       </c>
       <c r="B11" t="n">
-        <v>79766</v>
+        <v>57303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>102110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550706</v>
+        <v>550861</v>
       </c>
       <c r="R11" t="n">
-        <v>7245002</v>
+        <v>7245193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1761,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1791,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646878</v>
+        <v>122646853</v>
       </c>
       <c r="B12" t="n">
-        <v>97194</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550829</v>
+        <v>550761</v>
       </c>
       <c r="R12" t="n">
-        <v>7245185</v>
+        <v>7244876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646850</v>
+        <v>122646869</v>
       </c>
       <c r="B13" t="n">
-        <v>56593</v>
+        <v>74757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1920,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550760</v>
+        <v>550688</v>
       </c>
       <c r="R13" t="n">
-        <v>7244829</v>
+        <v>7245034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,11 +1984,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646824</v>
+        <v>122646866</v>
       </c>
       <c r="B14" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550678</v>
+        <v>550706</v>
       </c>
       <c r="R14" t="n">
-        <v>7244623</v>
+        <v>7245009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646849</v>
+        <v>122647145</v>
       </c>
       <c r="B15" t="n">
-        <v>90833</v>
+        <v>88192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550779</v>
+        <v>550855</v>
       </c>
       <c r="R15" t="n">
-        <v>7244796</v>
+        <v>7245196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2226,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647137</v>
+        <v>122647144</v>
       </c>
       <c r="B16" t="n">
-        <v>91182</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,25 +2238,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550827</v>
+        <v>550854</v>
       </c>
       <c r="R16" t="n">
-        <v>7245136</v>
+        <v>7245180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646822</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
-        <v>96108</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550659</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7244555</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646864</v>
+        <v>122646849</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550696</v>
+        <v>550779</v>
       </c>
       <c r="R18" t="n">
-        <v>7244978</v>
+        <v>7244796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647144</v>
+        <v>122646878</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>97194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550854</v>
+        <v>550829</v>
       </c>
       <c r="R19" t="n">
-        <v>7245180</v>
+        <v>7245185</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646872</v>
+        <v>122646856</v>
       </c>
       <c r="B20" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550828</v>
+        <v>550759</v>
       </c>
       <c r="R20" t="n">
-        <v>7245091</v>
+        <v>7244890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646868</v>
+        <v>122646821</v>
       </c>
       <c r="B21" t="n">
-        <v>74757</v>
+        <v>74752</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550694</v>
+        <v>550670</v>
       </c>
       <c r="R21" t="n">
-        <v>7245016</v>
+        <v>7244542</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646857</v>
+        <v>122646865</v>
       </c>
       <c r="B22" t="n">
-        <v>74762</v>
+        <v>79766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2874,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550751</v>
+        <v>550706</v>
       </c>
       <c r="R22" t="n">
-        <v>7244916</v>
+        <v>7245002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647146</v>
+        <v>122646823</v>
       </c>
       <c r="B23" t="n">
-        <v>57303</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102110</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550861</v>
+        <v>550677</v>
       </c>
       <c r="R23" t="n">
-        <v>7245193</v>
+        <v>7244586</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,17 +3038,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,7 +3063,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646845</v>
+        <v>122646848</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>91521</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3091,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550631</v>
+        <v>550776</v>
       </c>
       <c r="R24" t="n">
-        <v>7244710</v>
+        <v>7244797</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646853</v>
+        <v>122647136</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>91124</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550761</v>
+        <v>550831</v>
       </c>
       <c r="R25" t="n">
-        <v>7244876</v>
+        <v>7245134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,12 +3250,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,7 +3275,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3397,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646854</v>
+        <v>122646851</v>
       </c>
       <c r="B27" t="n">
-        <v>94641</v>
+        <v>74757</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3409,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550764</v>
+        <v>550748</v>
       </c>
       <c r="R27" t="n">
-        <v>7244897</v>
+        <v>7244855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646823</v>
+        <v>122647137</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>91182</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550677</v>
+        <v>550827</v>
       </c>
       <c r="R28" t="n">
-        <v>7244586</v>
+        <v>7245136</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,7 +3593,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3609,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122647138</v>
+        <v>122646863</v>
       </c>
       <c r="B29" t="n">
-        <v>90833</v>
+        <v>94653</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,25 +3616,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550832</v>
+        <v>550698</v>
       </c>
       <c r="R29" t="n">
-        <v>7245128</v>
+        <v>7244980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,12 +3674,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3699,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3715,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646855</v>
+        <v>122646850</v>
       </c>
       <c r="B30" t="n">
-        <v>94641</v>
+        <v>56593</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,21 +3726,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550770</v>
+        <v>550760</v>
       </c>
       <c r="R30" t="n">
-        <v>7244875</v>
+        <v>7244829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,6 +3786,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646808</v>
+        <v>122646855</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>94641</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550651</v>
+        <v>550770</v>
       </c>
       <c r="R31" t="n">
-        <v>7244779</v>
+        <v>7244875</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646861</v>
+        <v>122647126</v>
       </c>
       <c r="B32" t="n">
-        <v>74741</v>
+        <v>91124</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550710</v>
+        <v>550801</v>
       </c>
       <c r="R32" t="n">
-        <v>7244974</v>
+        <v>7244998</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122647136</v>
+        <v>122646852</v>
       </c>
       <c r="B33" t="n">
-        <v>91124</v>
+        <v>91521</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550831</v>
+        <v>550744</v>
       </c>
       <c r="R33" t="n">
-        <v>7245134</v>
+        <v>7244856</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646873</v>
+        <v>122646864</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550828</v>
+        <v>550696</v>
       </c>
       <c r="R34" t="n">
-        <v>7245125</v>
+        <v>7244978</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122647145</v>
+        <v>122646868</v>
       </c>
       <c r="B35" t="n">
-        <v>88192</v>
+        <v>74757</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550855</v>
+        <v>550694</v>
       </c>
       <c r="R35" t="n">
-        <v>7245196</v>
+        <v>7245016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4315,12 +4315,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646870</v>
+        <v>122646871</v>
       </c>
       <c r="B37" t="n">
-        <v>74752</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,21 +4473,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550726</v>
+        <v>550784</v>
       </c>
       <c r="R37" t="n">
-        <v>7245050</v>
+        <v>7245041</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646856</v>
+        <v>122646873</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550759</v>
+        <v>550828</v>
       </c>
       <c r="R38" t="n">
-        <v>7244890</v>
+        <v>7245125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122647126</v>
+        <v>122646822</v>
       </c>
       <c r="B39" t="n">
-        <v>91124</v>
+        <v>96108</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1841</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550801</v>
+        <v>550659</v>
       </c>
       <c r="R39" t="n">
-        <v>7244998</v>
+        <v>7244555</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646869</v>
+        <v>122647138</v>
       </c>
       <c r="B40" t="n">
-        <v>74757</v>
+        <v>90833</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550688</v>
+        <v>550832</v>
       </c>
       <c r="R40" t="n">
-        <v>7245034</v>
+        <v>7245128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646848</v>
+        <v>122646808</v>
       </c>
       <c r="B41" t="n">
-        <v>91521</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550776</v>
+        <v>550651</v>
       </c>
       <c r="R41" t="n">
-        <v>7244797</v>
+        <v>7244779</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646852</v>
+        <v>122646857</v>
       </c>
       <c r="B42" t="n">
-        <v>91521</v>
+        <v>74762</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550744</v>
+        <v>550751</v>
       </c>
       <c r="R42" t="n">
-        <v>7244856</v>
+        <v>7244916</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646871</v>
+        <v>122646870</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>74752</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550784</v>
+        <v>550726</v>
       </c>
       <c r="R43" t="n">
-        <v>7245041</v>
+        <v>7245050</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646851</v>
+        <v>122646824</v>
       </c>
       <c r="B44" t="n">
-        <v>74757</v>
+        <v>90833</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550748</v>
+        <v>550678</v>
       </c>
       <c r="R44" t="n">
-        <v>7244855</v>
+        <v>7244623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646863</v>
+        <v>122646872</v>
       </c>
       <c r="B45" t="n">
-        <v>94653</v>
+        <v>74757</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2813</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550698</v>
+        <v>550828</v>
       </c>
       <c r="R45" t="n">
-        <v>7244980</v>
+        <v>7245091</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646847</v>
+        <v>122646854</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>94641</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550746</v>
+        <v>550764</v>
       </c>
       <c r="R46" t="n">
-        <v>7244802</v>
+        <v>7244897</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646866</v>
+        <v>122646847</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550706</v>
+        <v>550746</v>
       </c>
       <c r="R47" t="n">
-        <v>7245009</v>
+        <v>7244802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646821</v>
+        <v>122646861</v>
       </c>
       <c r="B48" t="n">
-        <v>74752</v>
+        <v>74741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>310</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550670</v>
+        <v>550710</v>
       </c>
       <c r="R48" t="n">
-        <v>7244542</v>
+        <v>7244974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647146</v>
+        <v>122646846</v>
       </c>
       <c r="B11" t="n">
-        <v>57303</v>
+        <v>74758</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102110</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550861</v>
+        <v>550720</v>
       </c>
       <c r="R11" t="n">
-        <v>7245193</v>
+        <v>7244779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,17 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1802,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646853</v>
+        <v>122647126</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>91125</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550761</v>
+        <v>550801</v>
       </c>
       <c r="R12" t="n">
-        <v>7244876</v>
+        <v>7244998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,12 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,7 +1892,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1908,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646869</v>
+        <v>122646849</v>
       </c>
       <c r="B13" t="n">
-        <v>74757</v>
+        <v>90834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550688</v>
+        <v>550779</v>
       </c>
       <c r="R13" t="n">
-        <v>7245034</v>
+        <v>7244796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646866</v>
+        <v>122647138</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>90834</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550706</v>
+        <v>550832</v>
       </c>
       <c r="R14" t="n">
-        <v>7245009</v>
+        <v>7245128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647145</v>
+        <v>122646853</v>
       </c>
       <c r="B15" t="n">
-        <v>88192</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550855</v>
+        <v>550761</v>
       </c>
       <c r="R15" t="n">
-        <v>7245196</v>
+        <v>7244876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,12 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2210,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2226,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647144</v>
+        <v>122646848</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>91522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550854</v>
+        <v>550776</v>
       </c>
       <c r="R16" t="n">
-        <v>7245180</v>
+        <v>7244797</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2332,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646854</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>94642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550764</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7244897</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646849</v>
+        <v>122647144</v>
       </c>
       <c r="B18" t="n">
-        <v>90833</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550779</v>
+        <v>550854</v>
       </c>
       <c r="R18" t="n">
-        <v>7244796</v>
+        <v>7245180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,12 +2503,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,7 +2528,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2544,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646878</v>
+        <v>122646852</v>
       </c>
       <c r="B19" t="n">
-        <v>97194</v>
+        <v>91522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550829</v>
+        <v>550744</v>
       </c>
       <c r="R19" t="n">
-        <v>7245185</v>
+        <v>7244856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646856</v>
+        <v>122646850</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,25 +2657,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550759</v>
+        <v>550760</v>
       </c>
       <c r="R20" t="n">
-        <v>7244890</v>
+        <v>7244829</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2726,6 +2721,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646821</v>
+        <v>122646878</v>
       </c>
       <c r="B21" t="n">
-        <v>74752</v>
+        <v>97195</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,25 +2768,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>310</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550670</v>
+        <v>550829</v>
       </c>
       <c r="R21" t="n">
-        <v>7244542</v>
+        <v>7245185</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646865</v>
+        <v>122646821</v>
       </c>
       <c r="B22" t="n">
-        <v>79766</v>
+        <v>74753</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2874,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550706</v>
+        <v>550670</v>
       </c>
       <c r="R22" t="n">
-        <v>7245002</v>
+        <v>7244542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646823</v>
+        <v>122646868</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550677</v>
+        <v>550694</v>
       </c>
       <c r="R23" t="n">
-        <v>7244586</v>
+        <v>7245016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646848</v>
+        <v>122646851</v>
       </c>
       <c r="B24" t="n">
-        <v>91521</v>
+        <v>74758</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550776</v>
+        <v>550748</v>
       </c>
       <c r="R24" t="n">
-        <v>7244797</v>
+        <v>7244855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
         <v>122647136</v>
       </c>
       <c r="B25" t="n">
-        <v>91124</v>
+        <v>91125</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646846</v>
+        <v>122646824</v>
       </c>
       <c r="B26" t="n">
-        <v>74757</v>
+        <v>90834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550720</v>
+        <v>550678</v>
       </c>
       <c r="R26" t="n">
-        <v>7244779</v>
+        <v>7244623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646851</v>
+        <v>122646866</v>
       </c>
       <c r="B27" t="n">
-        <v>74757</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550748</v>
+        <v>550706</v>
       </c>
       <c r="R27" t="n">
-        <v>7244855</v>
+        <v>7245009</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122647137</v>
+        <v>122646861</v>
       </c>
       <c r="B28" t="n">
-        <v>91182</v>
+        <v>74742</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550827</v>
+        <v>550710</v>
       </c>
       <c r="R28" t="n">
-        <v>7245136</v>
+        <v>7244974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646863</v>
+        <v>122646855</v>
       </c>
       <c r="B29" t="n">
-        <v>94653</v>
+        <v>94642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550698</v>
+        <v>550770</v>
       </c>
       <c r="R29" t="n">
-        <v>7244980</v>
+        <v>7244875</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646850</v>
+        <v>122646872</v>
       </c>
       <c r="B30" t="n">
-        <v>56593</v>
+        <v>74758</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550760</v>
+        <v>550828</v>
       </c>
       <c r="R30" t="n">
-        <v>7244829</v>
+        <v>7245091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,11 +3786,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646855</v>
+        <v>122646870</v>
       </c>
       <c r="B31" t="n">
-        <v>94641</v>
+        <v>74753</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3828,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550770</v>
+        <v>550726</v>
       </c>
       <c r="R31" t="n">
-        <v>7244875</v>
+        <v>7245050</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122647126</v>
+        <v>122647145</v>
       </c>
       <c r="B32" t="n">
-        <v>91124</v>
+        <v>88193</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550801</v>
+        <v>550855</v>
       </c>
       <c r="R32" t="n">
-        <v>7244998</v>
+        <v>7245196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646852</v>
+        <v>122646823</v>
       </c>
       <c r="B33" t="n">
-        <v>91521</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4040,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550744</v>
+        <v>550677</v>
       </c>
       <c r="R33" t="n">
-        <v>7244856</v>
+        <v>7244586</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646864</v>
+        <v>122646874</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>74763</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4155,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550696</v>
+        <v>550824</v>
       </c>
       <c r="R34" t="n">
-        <v>7244978</v>
+        <v>7245149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646868</v>
+        <v>122647137</v>
       </c>
       <c r="B35" t="n">
-        <v>74757</v>
+        <v>91183</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4252,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550694</v>
+        <v>550827</v>
       </c>
       <c r="R35" t="n">
-        <v>7245016</v>
+        <v>7245136</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4315,12 +4310,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4340,7 +4335,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4351,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646874</v>
+        <v>122646871</v>
       </c>
       <c r="B36" t="n">
-        <v>74762</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4367,21 +4362,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550824</v>
+        <v>550784</v>
       </c>
       <c r="R36" t="n">
-        <v>7245149</v>
+        <v>7245041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646871</v>
+        <v>122646873</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>57495</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4464,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550784</v>
+        <v>550828</v>
       </c>
       <c r="R37" t="n">
-        <v>7245041</v>
+        <v>7245125</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646873</v>
+        <v>122646808</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>57495</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4603,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550828</v>
+        <v>550651</v>
       </c>
       <c r="R38" t="n">
-        <v>7245125</v>
+        <v>7244779</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646822</v>
+        <v>122646863</v>
       </c>
       <c r="B39" t="n">
-        <v>96108</v>
+        <v>94654</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,25 +4676,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1841</v>
+        <v>2813</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550659</v>
+        <v>550698</v>
       </c>
       <c r="R39" t="n">
-        <v>7244555</v>
+        <v>7244980</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122647138</v>
+        <v>122646865</v>
       </c>
       <c r="B40" t="n">
-        <v>90833</v>
+        <v>79767</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550832</v>
+        <v>550706</v>
       </c>
       <c r="R40" t="n">
-        <v>7245128</v>
+        <v>7245002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,12 +4840,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,7 +4865,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4881,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646808</v>
+        <v>122647146</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>57304</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4893,25 +4888,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>102110</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550651</v>
+        <v>550861</v>
       </c>
       <c r="R41" t="n">
-        <v>7244779</v>
+        <v>7245193</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4951,12 +4946,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646857</v>
+        <v>122646845</v>
       </c>
       <c r="B42" t="n">
-        <v>74762</v>
+        <v>78657</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550751</v>
+        <v>550631</v>
       </c>
       <c r="R42" t="n">
-        <v>7244916</v>
+        <v>7244710</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646870</v>
+        <v>122646857</v>
       </c>
       <c r="B43" t="n">
-        <v>74752</v>
+        <v>74763</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>310</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550726</v>
+        <v>550751</v>
       </c>
       <c r="R43" t="n">
-        <v>7245050</v>
+        <v>7244916</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646824</v>
+        <v>122646864</v>
       </c>
       <c r="B44" t="n">
-        <v>90833</v>
+        <v>78657</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550678</v>
+        <v>550696</v>
       </c>
       <c r="R44" t="n">
-        <v>7244623</v>
+        <v>7244978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646872</v>
+        <v>122646822</v>
       </c>
       <c r="B45" t="n">
-        <v>74757</v>
+        <v>96109</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1841</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550828</v>
+        <v>550659</v>
       </c>
       <c r="R45" t="n">
-        <v>7245091</v>
+        <v>7244555</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646854</v>
+        <v>122646869</v>
       </c>
       <c r="B46" t="n">
-        <v>94641</v>
+        <v>74758</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550764</v>
+        <v>550688</v>
       </c>
       <c r="R46" t="n">
-        <v>7244897</v>
+        <v>7245034</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
         <v>122646847</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646861</v>
+        <v>122646856</v>
       </c>
       <c r="B48" t="n">
-        <v>74741</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550710</v>
+        <v>550759</v>
       </c>
       <c r="R48" t="n">
-        <v>7244974</v>
+        <v>7244890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647144</v>
+        <v>122646852</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>91522</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550854</v>
+        <v>550744</v>
       </c>
       <c r="R18" t="n">
-        <v>7245180</v>
+        <v>7244856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646852</v>
+        <v>122646878</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>97195</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550744</v>
+        <v>550829</v>
       </c>
       <c r="R19" t="n">
-        <v>7244856</v>
+        <v>7245185</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646850</v>
+        <v>122647144</v>
       </c>
       <c r="B20" t="n">
-        <v>56594</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,25 +2657,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550760</v>
+        <v>550854</v>
       </c>
       <c r="R20" t="n">
-        <v>7244829</v>
+        <v>7245180</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,17 +2715,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2740,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2756,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646878</v>
+        <v>122646850</v>
       </c>
       <c r="B21" t="n">
-        <v>97195</v>
+        <v>56594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2767,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550829</v>
+        <v>550760</v>
       </c>
       <c r="R21" t="n">
-        <v>7245185</v>
+        <v>7244829</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646855</v>
+        <v>122646872</v>
       </c>
       <c r="B29" t="n">
-        <v>94642</v>
+        <v>74758</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3616,25 +3616,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550770</v>
+        <v>550828</v>
       </c>
       <c r="R29" t="n">
-        <v>7244875</v>
+        <v>7245091</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646872</v>
+        <v>122646855</v>
       </c>
       <c r="B30" t="n">
-        <v>74758</v>
+        <v>94642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550828</v>
+        <v>550770</v>
       </c>
       <c r="R30" t="n">
-        <v>7245091</v>
+        <v>7244875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646808</v>
+        <v>122646863</v>
       </c>
       <c r="B38" t="n">
-        <v>57495</v>
+        <v>94654</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>2813</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550651</v>
+        <v>550698</v>
       </c>
       <c r="R38" t="n">
-        <v>7244779</v>
+        <v>7244980</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646863</v>
+        <v>122646808</v>
       </c>
       <c r="B39" t="n">
-        <v>94654</v>
+        <v>57495</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2813</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550698</v>
+        <v>550651</v>
       </c>
       <c r="R39" t="n">
-        <v>7244980</v>
+        <v>7244779</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122647146</v>
+        <v>122646845</v>
       </c>
       <c r="B41" t="n">
-        <v>57304</v>
+        <v>78657</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102110</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550861</v>
+        <v>550631</v>
       </c>
       <c r="R41" t="n">
-        <v>7245193</v>
+        <v>7244710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,17 +4946,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4987,10 +4982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646845</v>
+        <v>122647146</v>
       </c>
       <c r="B42" t="n">
-        <v>78657</v>
+        <v>57304</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +4998,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>102110</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550631</v>
+        <v>550861</v>
       </c>
       <c r="R42" t="n">
-        <v>7244710</v>
+        <v>7245193</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,12 +5052,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646846</v>
+        <v>122646854</v>
       </c>
       <c r="B11" t="n">
-        <v>74758</v>
+        <v>94645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550720</v>
+        <v>550764</v>
       </c>
       <c r="R11" t="n">
-        <v>7244779</v>
+        <v>7244897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647126</v>
+        <v>122646873</v>
       </c>
       <c r="B12" t="n">
-        <v>91125</v>
+        <v>57495</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550801</v>
+        <v>550828</v>
       </c>
       <c r="R12" t="n">
-        <v>7244998</v>
+        <v>7245125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646849</v>
+        <v>122646846</v>
       </c>
       <c r="B13" t="n">
-        <v>90834</v>
+        <v>74761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550779</v>
+        <v>550720</v>
       </c>
       <c r="R13" t="n">
-        <v>7244796</v>
+        <v>7244779</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647138</v>
+        <v>122646847</v>
       </c>
       <c r="B14" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550832</v>
+        <v>550746</v>
       </c>
       <c r="R14" t="n">
-        <v>7245128</v>
+        <v>7244802</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646853</v>
+        <v>122646855</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>94645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550761</v>
+        <v>550770</v>
       </c>
       <c r="R15" t="n">
-        <v>7244876</v>
+        <v>7244875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646848</v>
+        <v>122646824</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>90837</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550776</v>
+        <v>550678</v>
       </c>
       <c r="R16" t="n">
-        <v>7244797</v>
+        <v>7244623</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646854</v>
+        <v>122647138</v>
       </c>
       <c r="B17" t="n">
-        <v>94642</v>
+        <v>90837</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550764</v>
+        <v>550832</v>
       </c>
       <c r="R17" t="n">
-        <v>7244897</v>
+        <v>7245128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646852</v>
+        <v>122646850</v>
       </c>
       <c r="B18" t="n">
-        <v>91522</v>
+        <v>56594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550744</v>
+        <v>550760</v>
       </c>
       <c r="R18" t="n">
-        <v>7244856</v>
+        <v>7244829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,6 +2509,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,7 +2547,7 @@
         <v>122646878</v>
       </c>
       <c r="B19" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2645,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647144</v>
+        <v>122646821</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>74756</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550854</v>
+        <v>550670</v>
       </c>
       <c r="R20" t="n">
-        <v>7245180</v>
+        <v>7244542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2740,7 +2745,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2751,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646850</v>
+        <v>122647126</v>
       </c>
       <c r="B21" t="n">
-        <v>56594</v>
+        <v>91128</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,25 +2768,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2791,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550760</v>
+        <v>550801</v>
       </c>
       <c r="R21" t="n">
-        <v>7244829</v>
+        <v>7244998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,17 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646821</v>
+        <v>122646856</v>
       </c>
       <c r="B22" t="n">
-        <v>74753</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550670</v>
+        <v>550759</v>
       </c>
       <c r="R22" t="n">
-        <v>7244542</v>
+        <v>7244890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646868</v>
+        <v>122646852</v>
       </c>
       <c r="B23" t="n">
-        <v>74758</v>
+        <v>91525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,25 +2980,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550694</v>
+        <v>550744</v>
       </c>
       <c r="R23" t="n">
-        <v>7245016</v>
+        <v>7244856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646851</v>
+        <v>122646872</v>
       </c>
       <c r="B24" t="n">
-        <v>74758</v>
+        <v>74761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550748</v>
+        <v>550828</v>
       </c>
       <c r="R24" t="n">
-        <v>7244855</v>
+        <v>7245091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122647136</v>
+        <v>122647145</v>
       </c>
       <c r="B25" t="n">
-        <v>91125</v>
+        <v>88196</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550831</v>
+        <v>550855</v>
       </c>
       <c r="R25" t="n">
-        <v>7245134</v>
+        <v>7245196</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646824</v>
+        <v>122646866</v>
       </c>
       <c r="B26" t="n">
-        <v>90834</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550678</v>
+        <v>550706</v>
       </c>
       <c r="R26" t="n">
-        <v>7244623</v>
+        <v>7245009</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646866</v>
+        <v>122646845</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550706</v>
+        <v>550631</v>
       </c>
       <c r="R27" t="n">
-        <v>7245009</v>
+        <v>7244710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646861</v>
+        <v>122646864</v>
       </c>
       <c r="B28" t="n">
-        <v>74742</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550710</v>
+        <v>550696</v>
       </c>
       <c r="R28" t="n">
-        <v>7244974</v>
+        <v>7244978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646872</v>
+        <v>122646853</v>
       </c>
       <c r="B29" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550828</v>
+        <v>550761</v>
       </c>
       <c r="R29" t="n">
-        <v>7245091</v>
+        <v>7244876</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646855</v>
+        <v>122646870</v>
       </c>
       <c r="B30" t="n">
-        <v>94642</v>
+        <v>74756</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550770</v>
+        <v>550726</v>
       </c>
       <c r="R30" t="n">
-        <v>7244875</v>
+        <v>7245050</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646870</v>
+        <v>122646822</v>
       </c>
       <c r="B31" t="n">
-        <v>74753</v>
+        <v>96112</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,21 +3832,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>310</v>
+        <v>1841</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550726</v>
+        <v>550659</v>
       </c>
       <c r="R31" t="n">
-        <v>7245050</v>
+        <v>7244555</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122647145</v>
+        <v>122646869</v>
       </c>
       <c r="B32" t="n">
-        <v>88193</v>
+        <v>74761</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550855</v>
+        <v>550688</v>
       </c>
       <c r="R32" t="n">
-        <v>7245196</v>
+        <v>7245034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4031,7 +4031,7 @@
         <v>122646823</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646874</v>
+        <v>122647136</v>
       </c>
       <c r="B34" t="n">
-        <v>74763</v>
+        <v>91128</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550824</v>
+        <v>550831</v>
       </c>
       <c r="R34" t="n">
-        <v>7245149</v>
+        <v>7245134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122647137</v>
+        <v>122646868</v>
       </c>
       <c r="B35" t="n">
-        <v>91183</v>
+        <v>74761</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4252,25 +4252,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550827</v>
+        <v>550694</v>
       </c>
       <c r="R35" t="n">
-        <v>7245136</v>
+        <v>7245016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4349,7 +4349,7 @@
         <v>122646871</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646873</v>
+        <v>122646857</v>
       </c>
       <c r="B37" t="n">
-        <v>57495</v>
+        <v>74766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>1467</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550828</v>
+        <v>550751</v>
       </c>
       <c r="R37" t="n">
-        <v>7245125</v>
+        <v>7244916</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4561,7 +4561,7 @@
         <v>122646863</v>
       </c>
       <c r="B38" t="n">
-        <v>94654</v>
+        <v>94657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646808</v>
+        <v>122646861</v>
       </c>
       <c r="B39" t="n">
-        <v>57495</v>
+        <v>74745</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>6439</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550651</v>
+        <v>550710</v>
       </c>
       <c r="R39" t="n">
-        <v>7244779</v>
+        <v>7244974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646865</v>
+        <v>122646808</v>
       </c>
       <c r="B40" t="n">
-        <v>79767</v>
+        <v>57495</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550706</v>
+        <v>550651</v>
       </c>
       <c r="R40" t="n">
-        <v>7245002</v>
+        <v>7244779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646845</v>
+        <v>122646874</v>
       </c>
       <c r="B41" t="n">
-        <v>78657</v>
+        <v>74766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550631</v>
+        <v>550824</v>
       </c>
       <c r="R41" t="n">
-        <v>7244710</v>
+        <v>7245149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122647146</v>
+        <v>122646851</v>
       </c>
       <c r="B42" t="n">
-        <v>57304</v>
+        <v>74761</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102110</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550861</v>
+        <v>550748</v>
       </c>
       <c r="R42" t="n">
-        <v>7245193</v>
+        <v>7244855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,17 +5052,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5077,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5093,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646857</v>
+        <v>122646865</v>
       </c>
       <c r="B43" t="n">
-        <v>74763</v>
+        <v>79770</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,25 +5100,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550751</v>
+        <v>550706</v>
       </c>
       <c r="R43" t="n">
-        <v>7244916</v>
+        <v>7245002</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646864</v>
+        <v>122646849</v>
       </c>
       <c r="B44" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5210,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550696</v>
+        <v>550779</v>
       </c>
       <c r="R44" t="n">
-        <v>7244978</v>
+        <v>7244796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646822</v>
+        <v>122647144</v>
       </c>
       <c r="B45" t="n">
-        <v>96109</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,21 +5316,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5340,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550659</v>
+        <v>550854</v>
       </c>
       <c r="R45" t="n">
-        <v>7244555</v>
+        <v>7245180</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,12 +5370,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,7 +5395,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5411,10 +5406,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646869</v>
+        <v>122646848</v>
       </c>
       <c r="B46" t="n">
-        <v>74758</v>
+        <v>91525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5418,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5446,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550688</v>
+        <v>550776</v>
       </c>
       <c r="R46" t="n">
-        <v>7245034</v>
+        <v>7244797</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5512,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646847</v>
+        <v>122647146</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>57304</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5528,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102110</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5552,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550746</v>
+        <v>550861</v>
       </c>
       <c r="R47" t="n">
-        <v>7244802</v>
+        <v>7245193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,12 +5582,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646856</v>
+        <v>122647137</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>91186</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550759</v>
+        <v>550827</v>
       </c>
       <c r="R48" t="n">
-        <v>7244890</v>
+        <v>7245136</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646854</v>
+        <v>122646823</v>
       </c>
       <c r="B11" t="n">
-        <v>94645</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550764</v>
+        <v>550677</v>
       </c>
       <c r="R11" t="n">
-        <v>7244897</v>
+        <v>7244586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646873</v>
+        <v>122646872</v>
       </c>
       <c r="B12" t="n">
-        <v>57495</v>
+        <v>74761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
         <v>550828</v>
       </c>
       <c r="R12" t="n">
-        <v>7245125</v>
+        <v>7245091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646846</v>
+        <v>122646856</v>
       </c>
       <c r="B13" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550720</v>
+        <v>550759</v>
       </c>
       <c r="R13" t="n">
-        <v>7244779</v>
+        <v>7244890</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646847</v>
+        <v>122647144</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550746</v>
+        <v>550854</v>
       </c>
       <c r="R14" t="n">
-        <v>7244802</v>
+        <v>7245180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646855</v>
+        <v>122646808</v>
       </c>
       <c r="B15" t="n">
-        <v>94645</v>
+        <v>57495</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550770</v>
+        <v>550651</v>
       </c>
       <c r="R15" t="n">
-        <v>7244875</v>
+        <v>7244779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646824</v>
+        <v>122646845</v>
       </c>
       <c r="B16" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550678</v>
+        <v>550631</v>
       </c>
       <c r="R16" t="n">
-        <v>7244623</v>
+        <v>7244710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647138</v>
+        <v>122646824</v>
       </c>
       <c r="B17" t="n">
         <v>90837</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550832</v>
+        <v>550678</v>
       </c>
       <c r="R17" t="n">
-        <v>7245128</v>
+        <v>7244623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646850</v>
+        <v>122646868</v>
       </c>
       <c r="B18" t="n">
-        <v>56594</v>
+        <v>74761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550760</v>
+        <v>550694</v>
       </c>
       <c r="R18" t="n">
-        <v>7244829</v>
+        <v>7245016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,11 +2509,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646878</v>
+        <v>122647138</v>
       </c>
       <c r="B19" t="n">
-        <v>97198</v>
+        <v>90837</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2551,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550829</v>
+        <v>550832</v>
       </c>
       <c r="R19" t="n">
-        <v>7245185</v>
+        <v>7245128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2650,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646821</v>
+        <v>122647146</v>
       </c>
       <c r="B20" t="n">
-        <v>74756</v>
+        <v>57304</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,21 +2661,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>310</v>
+        <v>102110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550670</v>
+        <v>550861</v>
       </c>
       <c r="R20" t="n">
-        <v>7244542</v>
+        <v>7245193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2715,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646856</v>
+        <v>122647137</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>91186</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2874,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550759</v>
+        <v>550827</v>
       </c>
       <c r="R22" t="n">
-        <v>7244890</v>
+        <v>7245136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646852</v>
+        <v>122646822</v>
       </c>
       <c r="B23" t="n">
-        <v>91525</v>
+        <v>96112</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,25 +2980,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1841</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550744</v>
+        <v>550659</v>
       </c>
       <c r="R23" t="n">
-        <v>7244856</v>
+        <v>7244555</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646872</v>
+        <v>122646854</v>
       </c>
       <c r="B24" t="n">
-        <v>74761</v>
+        <v>94645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550828</v>
+        <v>550764</v>
       </c>
       <c r="R24" t="n">
-        <v>7245091</v>
+        <v>7244897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122647145</v>
+        <v>122646864</v>
       </c>
       <c r="B25" t="n">
-        <v>88196</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550855</v>
+        <v>550696</v>
       </c>
       <c r="R25" t="n">
-        <v>7245196</v>
+        <v>7244978</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,12 +3250,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3286,7 +3286,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646866</v>
+        <v>122646853</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550706</v>
+        <v>550761</v>
       </c>
       <c r="R26" t="n">
-        <v>7245009</v>
+        <v>7244876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646845</v>
+        <v>122646852</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>91525</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550631</v>
+        <v>550744</v>
       </c>
       <c r="R27" t="n">
-        <v>7244710</v>
+        <v>7244856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646864</v>
+        <v>122646850</v>
       </c>
       <c r="B28" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550696</v>
+        <v>550760</v>
       </c>
       <c r="R28" t="n">
-        <v>7244978</v>
+        <v>7244829</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,6 +3574,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646853</v>
+        <v>122647136</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>91128</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550761</v>
+        <v>550831</v>
       </c>
       <c r="R29" t="n">
-        <v>7244876</v>
+        <v>7245134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,12 +3679,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,7 +3704,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3710,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646870</v>
+        <v>122646869</v>
       </c>
       <c r="B30" t="n">
-        <v>74756</v>
+        <v>74761</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3726,21 +3731,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550726</v>
+        <v>550688</v>
       </c>
       <c r="R30" t="n">
-        <v>7245050</v>
+        <v>7245034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646822</v>
+        <v>122646874</v>
       </c>
       <c r="B31" t="n">
-        <v>96112</v>
+        <v>74766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,21 +3837,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1841</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3856,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550659</v>
+        <v>550824</v>
       </c>
       <c r="R31" t="n">
-        <v>7244555</v>
+        <v>7245149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646869</v>
+        <v>122646857</v>
       </c>
       <c r="B32" t="n">
-        <v>74761</v>
+        <v>74766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3943,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550688</v>
+        <v>550751</v>
       </c>
       <c r="R32" t="n">
-        <v>7245034</v>
+        <v>7244916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4028,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646823</v>
+        <v>122646865</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>79770</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4040,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550677</v>
+        <v>550706</v>
       </c>
       <c r="R33" t="n">
-        <v>7244586</v>
+        <v>7245002</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4134,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122647136</v>
+        <v>122646863</v>
       </c>
       <c r="B34" t="n">
-        <v>91128</v>
+        <v>94657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4146,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550831</v>
+        <v>550698</v>
       </c>
       <c r="R34" t="n">
-        <v>7245134</v>
+        <v>7244980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,12 +4209,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4234,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646868</v>
+        <v>122646847</v>
       </c>
       <c r="B35" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4256,21 +4261,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550694</v>
+        <v>550746</v>
       </c>
       <c r="R35" t="n">
-        <v>7245016</v>
+        <v>7244802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4346,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646871</v>
+        <v>122646878</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4358,25 +4363,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550784</v>
+        <v>550829</v>
       </c>
       <c r="R36" t="n">
-        <v>7245041</v>
+        <v>7245185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646857</v>
+        <v>122646851</v>
       </c>
       <c r="B37" t="n">
-        <v>74766</v>
+        <v>74761</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4468,21 +4473,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4492,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550751</v>
+        <v>550748</v>
       </c>
       <c r="R37" t="n">
-        <v>7244916</v>
+        <v>7244855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646863</v>
+        <v>122646855</v>
       </c>
       <c r="B38" t="n">
-        <v>94657</v>
+        <v>94645</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4574,21 +4579,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550698</v>
+        <v>550770</v>
       </c>
       <c r="R38" t="n">
-        <v>7244980</v>
+        <v>7244875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646861</v>
+        <v>122646866</v>
       </c>
       <c r="B39" t="n">
-        <v>74745</v>
+        <v>78660</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4676,25 +4681,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550710</v>
+        <v>550706</v>
       </c>
       <c r="R39" t="n">
-        <v>7244974</v>
+        <v>7245009</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646808</v>
+        <v>122647145</v>
       </c>
       <c r="B40" t="n">
-        <v>57495</v>
+        <v>88196</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4782,25 +4787,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550651</v>
+        <v>550855</v>
       </c>
       <c r="R40" t="n">
-        <v>7244779</v>
+        <v>7245196</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4840,12 +4845,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,7 +4870,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4876,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646874</v>
+        <v>122646871</v>
       </c>
       <c r="B41" t="n">
-        <v>74766</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4916,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550824</v>
+        <v>550784</v>
       </c>
       <c r="R41" t="n">
-        <v>7245149</v>
+        <v>7245041</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646851</v>
+        <v>122646873</v>
       </c>
       <c r="B42" t="n">
-        <v>74761</v>
+        <v>57495</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4994,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5022,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550748</v>
+        <v>550828</v>
       </c>
       <c r="R42" t="n">
-        <v>7244855</v>
+        <v>7245125</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646865</v>
+        <v>122646846</v>
       </c>
       <c r="B43" t="n">
-        <v>79770</v>
+        <v>74761</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5100,25 +5105,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550706</v>
+        <v>550720</v>
       </c>
       <c r="R43" t="n">
-        <v>7245002</v>
+        <v>7244779</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646849</v>
+        <v>122646848</v>
       </c>
       <c r="B44" t="n">
-        <v>90837</v>
+        <v>91525</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5206,25 +5211,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550779</v>
+        <v>550776</v>
       </c>
       <c r="R44" t="n">
-        <v>7244796</v>
+        <v>7244797</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5300,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122647144</v>
+        <v>122646861</v>
       </c>
       <c r="B45" t="n">
-        <v>78660</v>
+        <v>74745</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5312,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5340,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550854</v>
+        <v>550710</v>
       </c>
       <c r="R45" t="n">
-        <v>7245180</v>
+        <v>7244974</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5370,12 +5375,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5395,7 +5400,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5406,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646848</v>
+        <v>122646849</v>
       </c>
       <c r="B46" t="n">
-        <v>91525</v>
+        <v>90837</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5418,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5446,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550776</v>
+        <v>550779</v>
       </c>
       <c r="R46" t="n">
-        <v>7244797</v>
+        <v>7244796</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5512,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122647146</v>
+        <v>122646821</v>
       </c>
       <c r="B47" t="n">
-        <v>57304</v>
+        <v>74756</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5528,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102110</v>
+        <v>310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5552,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550861</v>
+        <v>550670</v>
       </c>
       <c r="R47" t="n">
-        <v>7245193</v>
+        <v>7244542</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5582,17 +5587,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122647137</v>
+        <v>122646870</v>
       </c>
       <c r="B48" t="n">
-        <v>91186</v>
+        <v>74756</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2062</v>
+        <v>310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550827</v>
+        <v>550726</v>
       </c>
       <c r="R48" t="n">
-        <v>7245136</v>
+        <v>7245050</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646874</v>
+        <v>122646863</v>
       </c>
       <c r="B31" t="n">
-        <v>74766</v>
+        <v>94657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550824</v>
+        <v>550698</v>
       </c>
       <c r="R31" t="n">
-        <v>7245149</v>
+        <v>7244980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646857</v>
+        <v>122646865</v>
       </c>
       <c r="B32" t="n">
-        <v>74766</v>
+        <v>79770</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550751</v>
+        <v>550706</v>
       </c>
       <c r="R32" t="n">
-        <v>7244916</v>
+        <v>7245002</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646865</v>
+        <v>122646874</v>
       </c>
       <c r="B33" t="n">
-        <v>79770</v>
+        <v>74766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550706</v>
+        <v>550824</v>
       </c>
       <c r="R33" t="n">
-        <v>7245002</v>
+        <v>7245149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646863</v>
+        <v>122646857</v>
       </c>
       <c r="B34" t="n">
-        <v>94657</v>
+        <v>74766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550698</v>
+        <v>550751</v>
       </c>
       <c r="R34" t="n">
-        <v>7244980</v>
+        <v>7244916</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646851</v>
+        <v>122646855</v>
       </c>
       <c r="B37" t="n">
-        <v>74761</v>
+        <v>94645</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550748</v>
+        <v>550770</v>
       </c>
       <c r="R37" t="n">
-        <v>7244855</v>
+        <v>7244875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646855</v>
+        <v>122646851</v>
       </c>
       <c r="B38" t="n">
-        <v>94645</v>
+        <v>74761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550770</v>
+        <v>550748</v>
       </c>
       <c r="R38" t="n">
-        <v>7244875</v>
+        <v>7244855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646808</v>
+        <v>122646824</v>
       </c>
       <c r="B15" t="n">
-        <v>57495</v>
+        <v>90837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550651</v>
+        <v>550678</v>
       </c>
       <c r="R15" t="n">
-        <v>7244779</v>
+        <v>7244623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646845</v>
+        <v>122646868</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550631</v>
+        <v>550694</v>
       </c>
       <c r="R16" t="n">
-        <v>7244710</v>
+        <v>7245016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646824</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550678</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7244623</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646868</v>
+        <v>122646808</v>
       </c>
       <c r="B18" t="n">
-        <v>74761</v>
+        <v>57495</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550694</v>
+        <v>550651</v>
       </c>
       <c r="R18" t="n">
-        <v>7245016</v>
+        <v>7244779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646863</v>
+        <v>122646874</v>
       </c>
       <c r="B31" t="n">
-        <v>94657</v>
+        <v>74766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550698</v>
+        <v>550824</v>
       </c>
       <c r="R31" t="n">
-        <v>7244980</v>
+        <v>7245149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646865</v>
+        <v>122646857</v>
       </c>
       <c r="B32" t="n">
-        <v>79770</v>
+        <v>74766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550706</v>
+        <v>550751</v>
       </c>
       <c r="R32" t="n">
-        <v>7245002</v>
+        <v>7244916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646874</v>
+        <v>122646865</v>
       </c>
       <c r="B33" t="n">
-        <v>74766</v>
+        <v>79770</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550824</v>
+        <v>550706</v>
       </c>
       <c r="R33" t="n">
-        <v>7245149</v>
+        <v>7245002</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646857</v>
+        <v>122646863</v>
       </c>
       <c r="B34" t="n">
-        <v>74766</v>
+        <v>94657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550751</v>
+        <v>550698</v>
       </c>
       <c r="R34" t="n">
-        <v>7244916</v>
+        <v>7244980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646847</v>
+        <v>122646878</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550746</v>
+        <v>550829</v>
       </c>
       <c r="R35" t="n">
-        <v>7244802</v>
+        <v>7245185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646878</v>
+        <v>122646847</v>
       </c>
       <c r="B36" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550829</v>
+        <v>550746</v>
       </c>
       <c r="R36" t="n">
-        <v>7245185</v>
+        <v>7244802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646824</v>
+        <v>122646808</v>
       </c>
       <c r="B15" t="n">
-        <v>90837</v>
+        <v>57495</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550678</v>
+        <v>550651</v>
       </c>
       <c r="R15" t="n">
-        <v>7244623</v>
+        <v>7244779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646868</v>
+        <v>122646845</v>
       </c>
       <c r="B16" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550694</v>
+        <v>550631</v>
       </c>
       <c r="R16" t="n">
-        <v>7245016</v>
+        <v>7244710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646824</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550678</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7244623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646808</v>
+        <v>122646868</v>
       </c>
       <c r="B18" t="n">
-        <v>57495</v>
+        <v>74761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550651</v>
+        <v>550694</v>
       </c>
       <c r="R18" t="n">
-        <v>7244779</v>
+        <v>7245016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646874</v>
+        <v>122646863</v>
       </c>
       <c r="B31" t="n">
-        <v>74766</v>
+        <v>94657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550824</v>
+        <v>550698</v>
       </c>
       <c r="R31" t="n">
-        <v>7245149</v>
+        <v>7244980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646857</v>
+        <v>122646865</v>
       </c>
       <c r="B32" t="n">
-        <v>74766</v>
+        <v>79770</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550751</v>
+        <v>550706</v>
       </c>
       <c r="R32" t="n">
-        <v>7244916</v>
+        <v>7245002</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646865</v>
+        <v>122646874</v>
       </c>
       <c r="B33" t="n">
-        <v>79770</v>
+        <v>74766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550706</v>
+        <v>550824</v>
       </c>
       <c r="R33" t="n">
-        <v>7245002</v>
+        <v>7245149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646863</v>
+        <v>122646857</v>
       </c>
       <c r="B34" t="n">
-        <v>94657</v>
+        <v>74766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550698</v>
+        <v>550751</v>
       </c>
       <c r="R34" t="n">
-        <v>7244980</v>
+        <v>7244916</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646878</v>
+        <v>122646847</v>
       </c>
       <c r="B35" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550829</v>
+        <v>550746</v>
       </c>
       <c r="R35" t="n">
-        <v>7245185</v>
+        <v>7244802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646847</v>
+        <v>122646878</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550746</v>
+        <v>550829</v>
       </c>
       <c r="R36" t="n">
-        <v>7244802</v>
+        <v>7245185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646855</v>
+        <v>122646851</v>
       </c>
       <c r="B37" t="n">
-        <v>94645</v>
+        <v>74761</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550770</v>
+        <v>550748</v>
       </c>
       <c r="R37" t="n">
-        <v>7244875</v>
+        <v>7244855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646851</v>
+        <v>122646855</v>
       </c>
       <c r="B38" t="n">
-        <v>74761</v>
+        <v>94645</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550748</v>
+        <v>550770</v>
       </c>
       <c r="R38" t="n">
-        <v>7244855</v>
+        <v>7244875</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646808</v>
+        <v>122646824</v>
       </c>
       <c r="B15" t="n">
-        <v>57495</v>
+        <v>90837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550651</v>
+        <v>550678</v>
       </c>
       <c r="R15" t="n">
-        <v>7244779</v>
+        <v>7244623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646845</v>
+        <v>122646868</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550631</v>
+        <v>550694</v>
       </c>
       <c r="R16" t="n">
-        <v>7244710</v>
+        <v>7245016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646824</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550678</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7244623</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646868</v>
+        <v>122646808</v>
       </c>
       <c r="B18" t="n">
-        <v>74761</v>
+        <v>57495</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550694</v>
+        <v>550651</v>
       </c>
       <c r="R18" t="n">
-        <v>7245016</v>
+        <v>7244779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646824</v>
+        <v>122646808</v>
       </c>
       <c r="B15" t="n">
-        <v>90837</v>
+        <v>57495</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550678</v>
+        <v>550651</v>
       </c>
       <c r="R15" t="n">
-        <v>7244623</v>
+        <v>7244779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646868</v>
+        <v>122646845</v>
       </c>
       <c r="B16" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550694</v>
+        <v>550631</v>
       </c>
       <c r="R16" t="n">
-        <v>7245016</v>
+        <v>7244710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646824</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550678</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7244623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646808</v>
+        <v>122646868</v>
       </c>
       <c r="B18" t="n">
-        <v>57495</v>
+        <v>74761</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550651</v>
+        <v>550694</v>
       </c>
       <c r="R18" t="n">
-        <v>7244779</v>
+        <v>7245016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646847</v>
+        <v>122646878</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550746</v>
+        <v>550829</v>
       </c>
       <c r="R35" t="n">
-        <v>7244802</v>
+        <v>7245185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646878</v>
+        <v>122646847</v>
       </c>
       <c r="B36" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550829</v>
+        <v>550746</v>
       </c>
       <c r="R36" t="n">
-        <v>7245185</v>
+        <v>7244802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646851</v>
+        <v>122646855</v>
       </c>
       <c r="B37" t="n">
-        <v>74761</v>
+        <v>94645</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550748</v>
+        <v>550770</v>
       </c>
       <c r="R37" t="n">
-        <v>7244855</v>
+        <v>7244875</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646855</v>
+        <v>122646851</v>
       </c>
       <c r="B38" t="n">
-        <v>94645</v>
+        <v>74761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550770</v>
+        <v>550748</v>
       </c>
       <c r="R38" t="n">
-        <v>7244875</v>
+        <v>7244855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646808</v>
+        <v>122646824</v>
       </c>
       <c r="B15" t="n">
-        <v>57495</v>
+        <v>90837</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550651</v>
+        <v>550678</v>
       </c>
       <c r="R15" t="n">
-        <v>7244779</v>
+        <v>7244623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646845</v>
+        <v>122646868</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550631</v>
+        <v>550694</v>
       </c>
       <c r="R16" t="n">
-        <v>7244710</v>
+        <v>7245016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646824</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550678</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7244623</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646868</v>
+        <v>122646808</v>
       </c>
       <c r="B18" t="n">
-        <v>74761</v>
+        <v>57495</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550694</v>
+        <v>550651</v>
       </c>
       <c r="R18" t="n">
-        <v>7245016</v>
+        <v>7244779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646863</v>
+        <v>122646874</v>
       </c>
       <c r="B31" t="n">
-        <v>94657</v>
+        <v>74766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550698</v>
+        <v>550824</v>
       </c>
       <c r="R31" t="n">
-        <v>7244980</v>
+        <v>7245149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646865</v>
+        <v>122646857</v>
       </c>
       <c r="B32" t="n">
-        <v>79770</v>
+        <v>74766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550706</v>
+        <v>550751</v>
       </c>
       <c r="R32" t="n">
-        <v>7245002</v>
+        <v>7244916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646874</v>
+        <v>122646865</v>
       </c>
       <c r="B33" t="n">
-        <v>74766</v>
+        <v>79770</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550824</v>
+        <v>550706</v>
       </c>
       <c r="R33" t="n">
-        <v>7245149</v>
+        <v>7245002</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646857</v>
+        <v>122646863</v>
       </c>
       <c r="B34" t="n">
-        <v>74766</v>
+        <v>94657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1467</v>
+        <v>2813</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550751</v>
+        <v>550698</v>
       </c>
       <c r="R34" t="n">
-        <v>7244916</v>
+        <v>7244980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646878</v>
+        <v>122646847</v>
       </c>
       <c r="B35" t="n">
-        <v>97198</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550829</v>
+        <v>550746</v>
       </c>
       <c r="R35" t="n">
-        <v>7245185</v>
+        <v>7244802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646847</v>
+        <v>122646878</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>97198</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550746</v>
+        <v>550829</v>
       </c>
       <c r="R36" t="n">
-        <v>7244802</v>
+        <v>7245185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646823</v>
+        <v>122647138</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550677</v>
+        <v>550832</v>
       </c>
       <c r="R11" t="n">
-        <v>7244586</v>
+        <v>7245128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646872</v>
+        <v>122646866</v>
       </c>
       <c r="B12" t="n">
-        <v>74761</v>
+        <v>78762</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550828</v>
+        <v>550706</v>
       </c>
       <c r="R12" t="n">
-        <v>7245091</v>
+        <v>7245009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646856</v>
+        <v>122646871</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550759</v>
+        <v>550784</v>
       </c>
       <c r="R13" t="n">
-        <v>7244890</v>
+        <v>7245041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647144</v>
+        <v>122646824</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>90940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550854</v>
+        <v>550678</v>
       </c>
       <c r="R14" t="n">
-        <v>7245180</v>
+        <v>7244623</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646824</v>
+        <v>122646848</v>
       </c>
       <c r="B15" t="n">
-        <v>90837</v>
+        <v>91628</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550678</v>
+        <v>550776</v>
       </c>
       <c r="R15" t="n">
-        <v>7244623</v>
+        <v>7244797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646868</v>
+        <v>122647126</v>
       </c>
       <c r="B16" t="n">
-        <v>74761</v>
+        <v>91231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550694</v>
+        <v>550801</v>
       </c>
       <c r="R16" t="n">
-        <v>7245016</v>
+        <v>7244998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646878</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>97301</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550829</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7245185</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646808</v>
+        <v>122646861</v>
       </c>
       <c r="B18" t="n">
-        <v>57495</v>
+        <v>74847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550651</v>
+        <v>550710</v>
       </c>
       <c r="R18" t="n">
-        <v>7244779</v>
+        <v>7244974</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647138</v>
+        <v>122646870</v>
       </c>
       <c r="B19" t="n">
-        <v>90837</v>
+        <v>74858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550832</v>
+        <v>550726</v>
       </c>
       <c r="R19" t="n">
-        <v>7245128</v>
+        <v>7245050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647146</v>
+        <v>122646852</v>
       </c>
       <c r="B20" t="n">
-        <v>57304</v>
+        <v>91628</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,25 +2657,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102110</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550861</v>
+        <v>550744</v>
       </c>
       <c r="R20" t="n">
-        <v>7245193</v>
+        <v>7244856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,17 +2715,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2740,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2756,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647126</v>
+        <v>122646868</v>
       </c>
       <c r="B21" t="n">
-        <v>91128</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2767,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550801</v>
+        <v>550694</v>
       </c>
       <c r="R21" t="n">
-        <v>7244998</v>
+        <v>7245016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2821,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,7 +2846,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647137</v>
+        <v>122646823</v>
       </c>
       <c r="B22" t="n">
-        <v>91186</v>
+        <v>78762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2869,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550827</v>
+        <v>550677</v>
       </c>
       <c r="R22" t="n">
-        <v>7245136</v>
+        <v>7244586</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,12 +2927,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,7 +2952,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2968,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646822</v>
+        <v>122646808</v>
       </c>
       <c r="B23" t="n">
-        <v>96112</v>
+        <v>57589</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,25 +2975,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1841</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550659</v>
+        <v>550651</v>
       </c>
       <c r="R23" t="n">
-        <v>7244555</v>
+        <v>7244779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646854</v>
+        <v>122646857</v>
       </c>
       <c r="B24" t="n">
-        <v>94645</v>
+        <v>74868</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3081,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550764</v>
+        <v>550751</v>
       </c>
       <c r="R24" t="n">
-        <v>7244897</v>
+        <v>7244916</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646864</v>
+        <v>122646855</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>94748</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3187,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550696</v>
+        <v>550770</v>
       </c>
       <c r="R25" t="n">
-        <v>7244978</v>
+        <v>7244875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646853</v>
+        <v>122646851</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,21 +3297,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550761</v>
+        <v>550748</v>
       </c>
       <c r="R26" t="n">
-        <v>7244876</v>
+        <v>7244855</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646852</v>
+        <v>122647137</v>
       </c>
       <c r="B27" t="n">
-        <v>91525</v>
+        <v>91289</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3399,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550744</v>
+        <v>550827</v>
       </c>
       <c r="R27" t="n">
-        <v>7244856</v>
+        <v>7245136</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,12 +3457,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,7 +3482,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3498,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646850</v>
+        <v>122646874</v>
       </c>
       <c r="B28" t="n">
-        <v>56594</v>
+        <v>74868</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3505,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550760</v>
+        <v>550824</v>
       </c>
       <c r="R28" t="n">
-        <v>7244829</v>
+        <v>7245149</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,11 +3569,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122647136</v>
+        <v>122646854</v>
       </c>
       <c r="B29" t="n">
-        <v>91128</v>
+        <v>94748</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,25 +3611,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550831</v>
+        <v>550764</v>
       </c>
       <c r="R29" t="n">
-        <v>7245134</v>
+        <v>7244897</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3679,12 +3669,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,7 +3694,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3715,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646869</v>
+        <v>122647146</v>
       </c>
       <c r="B30" t="n">
-        <v>74761</v>
+        <v>57398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>102110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3755,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550688</v>
+        <v>550861</v>
       </c>
       <c r="R30" t="n">
-        <v>7245034</v>
+        <v>7245193</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,12 +3775,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,7 +3805,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3821,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646874</v>
+        <v>122646822</v>
       </c>
       <c r="B31" t="n">
-        <v>74766</v>
+        <v>96215</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,21 +3832,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>1841</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550824</v>
+        <v>550659</v>
       </c>
       <c r="R31" t="n">
-        <v>7245149</v>
+        <v>7244555</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646857</v>
+        <v>122646869</v>
       </c>
       <c r="B32" t="n">
-        <v>74766</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550751</v>
+        <v>550688</v>
       </c>
       <c r="R32" t="n">
-        <v>7244916</v>
+        <v>7245034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646865</v>
+        <v>122646864</v>
       </c>
       <c r="B33" t="n">
-        <v>79770</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4040,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550706</v>
+        <v>550696</v>
       </c>
       <c r="R33" t="n">
-        <v>7245002</v>
+        <v>7244978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646863</v>
+        <v>122647144</v>
       </c>
       <c r="B34" t="n">
-        <v>94657</v>
+        <v>78762</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4146,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550698</v>
+        <v>550854</v>
       </c>
       <c r="R34" t="n">
-        <v>7244980</v>
+        <v>7245180</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,12 +4204,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4234,7 +4229,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4245,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646847</v>
+        <v>122646872</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4261,21 +4256,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550746</v>
+        <v>550828</v>
       </c>
       <c r="R35" t="n">
-        <v>7244802</v>
+        <v>7245091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646878</v>
+        <v>122647145</v>
       </c>
       <c r="B36" t="n">
-        <v>97198</v>
+        <v>88299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4358,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550829</v>
+        <v>550855</v>
       </c>
       <c r="R36" t="n">
-        <v>7245185</v>
+        <v>7245196</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4421,12 +4416,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4446,7 +4441,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4457,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646855</v>
+        <v>122646845</v>
       </c>
       <c r="B37" t="n">
-        <v>94645</v>
+        <v>78762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4464,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550770</v>
+        <v>550631</v>
       </c>
       <c r="R37" t="n">
-        <v>7244875</v>
+        <v>7244710</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646851</v>
+        <v>122646850</v>
       </c>
       <c r="B38" t="n">
-        <v>74761</v>
+        <v>56688</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4570,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550748</v>
+        <v>550760</v>
       </c>
       <c r="R38" t="n">
-        <v>7244855</v>
+        <v>7244829</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4639,6 +4634,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646866</v>
+        <v>122646873</v>
       </c>
       <c r="B39" t="n">
-        <v>78660</v>
+        <v>57589</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550706</v>
+        <v>550828</v>
       </c>
       <c r="R39" t="n">
-        <v>7245009</v>
+        <v>7245125</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122647145</v>
+        <v>122647136</v>
       </c>
       <c r="B40" t="n">
-        <v>88196</v>
+        <v>91231</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550855</v>
+        <v>550831</v>
       </c>
       <c r="R40" t="n">
-        <v>7245196</v>
+        <v>7245134</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646871</v>
+        <v>122646847</v>
       </c>
       <c r="B41" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550784</v>
+        <v>550746</v>
       </c>
       <c r="R41" t="n">
-        <v>7245041</v>
+        <v>7244802</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646873</v>
+        <v>122646863</v>
       </c>
       <c r="B42" t="n">
-        <v>57495</v>
+        <v>94760</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>2813</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550828</v>
+        <v>550698</v>
       </c>
       <c r="R42" t="n">
-        <v>7245125</v>
+        <v>7244980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646846</v>
+        <v>122646849</v>
       </c>
       <c r="B43" t="n">
-        <v>74761</v>
+        <v>90940</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550720</v>
+        <v>550779</v>
       </c>
       <c r="R43" t="n">
-        <v>7244779</v>
+        <v>7244796</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646848</v>
+        <v>122646856</v>
       </c>
       <c r="B44" t="n">
-        <v>91525</v>
+        <v>78762</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5211,25 +5211,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550776</v>
+        <v>550759</v>
       </c>
       <c r="R44" t="n">
-        <v>7244797</v>
+        <v>7244890</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646861</v>
+        <v>122646865</v>
       </c>
       <c r="B45" t="n">
-        <v>74745</v>
+        <v>79872</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550710</v>
+        <v>550706</v>
       </c>
       <c r="R45" t="n">
-        <v>7244974</v>
+        <v>7245002</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646849</v>
+        <v>122646821</v>
       </c>
       <c r="B46" t="n">
-        <v>90837</v>
+        <v>74858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550779</v>
+        <v>550670</v>
       </c>
       <c r="R46" t="n">
-        <v>7244796</v>
+        <v>7244542</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646821</v>
+        <v>122646846</v>
       </c>
       <c r="B47" t="n">
-        <v>74756</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550670</v>
+        <v>550720</v>
       </c>
       <c r="R47" t="n">
-        <v>7244542</v>
+        <v>7244779</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646870</v>
+        <v>122646853</v>
       </c>
       <c r="B48" t="n">
-        <v>74756</v>
+        <v>78762</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550726</v>
+        <v>550761</v>
       </c>
       <c r="R48" t="n">
-        <v>7245050</v>
+        <v>7244876</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647126</v>
+        <v>122646878</v>
       </c>
       <c r="B16" t="n">
-        <v>91231</v>
+        <v>97301</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550801</v>
+        <v>550829</v>
       </c>
       <c r="R16" t="n">
-        <v>7244998</v>
+        <v>7245185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646878</v>
+        <v>122647126</v>
       </c>
       <c r="B17" t="n">
-        <v>97301</v>
+        <v>91231</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550829</v>
+        <v>550801</v>
       </c>
       <c r="R17" t="n">
-        <v>7245185</v>
+        <v>7244998</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3175,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646855</v>
+        <v>122646851</v>
       </c>
       <c r="B25" t="n">
-        <v>94748</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,25 +3187,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550770</v>
+        <v>550748</v>
       </c>
       <c r="R25" t="n">
-        <v>7244875</v>
+        <v>7244855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646851</v>
+        <v>122646855</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>94748</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550748</v>
+        <v>550770</v>
       </c>
       <c r="R26" t="n">
-        <v>7244855</v>
+        <v>7244875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122647146</v>
+        <v>122646822</v>
       </c>
       <c r="B30" t="n">
-        <v>57398</v>
+        <v>96215</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102110</v>
+        <v>1841</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550861</v>
+        <v>550659</v>
       </c>
       <c r="R30" t="n">
-        <v>7245193</v>
+        <v>7244555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,17 +3775,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3805,7 +3800,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3816,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646822</v>
+        <v>122646869</v>
       </c>
       <c r="B31" t="n">
-        <v>96215</v>
+        <v>74863</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1841</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3856,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550659</v>
+        <v>550688</v>
       </c>
       <c r="R31" t="n">
-        <v>7244555</v>
+        <v>7245034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646869</v>
+        <v>122646864</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>78762</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3933,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550688</v>
+        <v>550696</v>
       </c>
       <c r="R32" t="n">
-        <v>7245034</v>
+        <v>7244978</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4028,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646864</v>
+        <v>122647144</v>
       </c>
       <c r="B33" t="n">
         <v>78762</v>
@@ -4068,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550696</v>
+        <v>550854</v>
       </c>
       <c r="R33" t="n">
-        <v>7244978</v>
+        <v>7245180</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,12 +4093,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4123,7 +4118,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4134,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122647144</v>
+        <v>122646872</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4150,21 +4145,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550854</v>
+        <v>550828</v>
       </c>
       <c r="R34" t="n">
-        <v>7245180</v>
+        <v>7245091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,12 +4199,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4224,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646872</v>
+        <v>122647146</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>57398</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4256,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>102110</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550828</v>
+        <v>550861</v>
       </c>
       <c r="R35" t="n">
-        <v>7245091</v>
+        <v>7245193</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,12 +4305,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647138</v>
+        <v>122646870</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>74858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550832</v>
+        <v>550726</v>
       </c>
       <c r="R11" t="n">
-        <v>7245128</v>
+        <v>7245050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646866</v>
+        <v>122646852</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>91632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550706</v>
+        <v>550744</v>
       </c>
       <c r="R12" t="n">
-        <v>7245009</v>
+        <v>7244856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646871</v>
+        <v>122646869</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550784</v>
+        <v>550688</v>
       </c>
       <c r="R13" t="n">
-        <v>7245041</v>
+        <v>7245034</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646824</v>
+        <v>122646878</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>97309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550678</v>
+        <v>550829</v>
       </c>
       <c r="R14" t="n">
-        <v>7244623</v>
+        <v>7245185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646848</v>
+        <v>122646861</v>
       </c>
       <c r="B15" t="n">
-        <v>91628</v>
+        <v>74847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550776</v>
+        <v>550710</v>
       </c>
       <c r="R15" t="n">
-        <v>7244797</v>
+        <v>7244974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646878</v>
+        <v>122646845</v>
       </c>
       <c r="B16" t="n">
-        <v>97301</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550829</v>
+        <v>550631</v>
       </c>
       <c r="R16" t="n">
-        <v>7245185</v>
+        <v>7244710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647126</v>
+        <v>122646864</v>
       </c>
       <c r="B17" t="n">
-        <v>91231</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550801</v>
+        <v>550696</v>
       </c>
       <c r="R17" t="n">
-        <v>7244998</v>
+        <v>7244978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646861</v>
+        <v>122647146</v>
       </c>
       <c r="B18" t="n">
-        <v>74847</v>
+        <v>57398</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>102110</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550710</v>
+        <v>550861</v>
       </c>
       <c r="R18" t="n">
-        <v>7244974</v>
+        <v>7245193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,12 +2503,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2533,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2539,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646870</v>
+        <v>122646849</v>
       </c>
       <c r="B19" t="n">
-        <v>74858</v>
+        <v>90944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2560,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550726</v>
+        <v>550779</v>
       </c>
       <c r="R19" t="n">
-        <v>7245050</v>
+        <v>7244796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646852</v>
+        <v>122647144</v>
       </c>
       <c r="B20" t="n">
-        <v>91628</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550744</v>
+        <v>550854</v>
       </c>
       <c r="R20" t="n">
-        <v>7244856</v>
+        <v>7245180</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,12 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2740,7 +2745,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2751,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646868</v>
+        <v>122646871</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,21 +2772,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2791,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550694</v>
+        <v>550784</v>
       </c>
       <c r="R21" t="n">
-        <v>7245016</v>
+        <v>7245041</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646823</v>
+        <v>122646853</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550677</v>
+        <v>550761</v>
       </c>
       <c r="R22" t="n">
-        <v>7244586</v>
+        <v>7244876</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646808</v>
+        <v>122646850</v>
       </c>
       <c r="B23" t="n">
-        <v>57589</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550651</v>
+        <v>550760</v>
       </c>
       <c r="R23" t="n">
-        <v>7244779</v>
+        <v>7244829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,6 +3044,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646857</v>
+        <v>122646851</v>
       </c>
       <c r="B24" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,21 +3095,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3109,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550751</v>
+        <v>550748</v>
       </c>
       <c r="R24" t="n">
-        <v>7244916</v>
+        <v>7244855</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646851</v>
+        <v>122646854</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>94756</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,25 +3197,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550748</v>
+        <v>550764</v>
       </c>
       <c r="R25" t="n">
-        <v>7244855</v>
+        <v>7244897</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646855</v>
+        <v>122647138</v>
       </c>
       <c r="B26" t="n">
-        <v>94748</v>
+        <v>90944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550770</v>
+        <v>550832</v>
       </c>
       <c r="R26" t="n">
-        <v>7244875</v>
+        <v>7245128</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,12 +3361,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,7 +3386,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3387,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122647137</v>
+        <v>122646856</v>
       </c>
       <c r="B27" t="n">
-        <v>91289</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3399,25 +3409,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550827</v>
+        <v>550759</v>
       </c>
       <c r="R27" t="n">
-        <v>7245136</v>
+        <v>7244890</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,12 +3467,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,7 +3492,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3493,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646874</v>
+        <v>122646847</v>
       </c>
       <c r="B28" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,21 +3519,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550824</v>
+        <v>550746</v>
       </c>
       <c r="R28" t="n">
-        <v>7245149</v>
+        <v>7244802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646854</v>
+        <v>122646863</v>
       </c>
       <c r="B29" t="n">
-        <v>94748</v>
+        <v>94768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550764</v>
+        <v>550698</v>
       </c>
       <c r="R29" t="n">
-        <v>7244897</v>
+        <v>7244980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646822</v>
+        <v>122647145</v>
       </c>
       <c r="B30" t="n">
-        <v>96215</v>
+        <v>88303</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3731,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1841</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550659</v>
+        <v>550855</v>
       </c>
       <c r="R30" t="n">
-        <v>7244555</v>
+        <v>7245196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,12 +3785,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,7 +3810,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3811,7 +3821,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646869</v>
+        <v>122646846</v>
       </c>
       <c r="B31" t="n">
         <v>74863</v>
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550688</v>
+        <v>550720</v>
       </c>
       <c r="R31" t="n">
-        <v>7245034</v>
+        <v>7244779</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646864</v>
+        <v>122646855</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>94756</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550696</v>
+        <v>550770</v>
       </c>
       <c r="R32" t="n">
-        <v>7244978</v>
+        <v>7244875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122647144</v>
+        <v>122646822</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>96223</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,21 +4049,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550854</v>
+        <v>550659</v>
       </c>
       <c r="R33" t="n">
-        <v>7245180</v>
+        <v>7244555</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4093,12 +4103,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,7 +4128,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4129,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646872</v>
+        <v>122646808</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4141,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550828</v>
+        <v>550651</v>
       </c>
       <c r="R34" t="n">
-        <v>7245091</v>
+        <v>7244779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4235,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122647146</v>
+        <v>122646823</v>
       </c>
       <c r="B35" t="n">
-        <v>57398</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4251,21 +4261,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102110</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4275,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550861</v>
+        <v>550677</v>
       </c>
       <c r="R35" t="n">
-        <v>7245193</v>
+        <v>7244586</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4305,17 +4315,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4340,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4346,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122647145</v>
+        <v>122646857</v>
       </c>
       <c r="B36" t="n">
-        <v>88299</v>
+        <v>74868</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4362,21 +4367,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550855</v>
+        <v>550751</v>
       </c>
       <c r="R36" t="n">
-        <v>7245196</v>
+        <v>7244916</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4416,12 +4421,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4441,7 +4446,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4452,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646845</v>
+        <v>122646873</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>57589</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4464,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4492,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550631</v>
+        <v>550828</v>
       </c>
       <c r="R37" t="n">
-        <v>7244710</v>
+        <v>7245125</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646850</v>
+        <v>122646866</v>
       </c>
       <c r="B38" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4570,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550760</v>
+        <v>550706</v>
       </c>
       <c r="R38" t="n">
-        <v>7244829</v>
+        <v>7245009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4634,11 +4639,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646873</v>
+        <v>122646848</v>
       </c>
       <c r="B39" t="n">
-        <v>57589</v>
+        <v>91632</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550828</v>
+        <v>550776</v>
       </c>
       <c r="R39" t="n">
-        <v>7245125</v>
+        <v>7244797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122647136</v>
+        <v>122646872</v>
       </c>
       <c r="B40" t="n">
-        <v>91231</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550831</v>
+        <v>550828</v>
       </c>
       <c r="R40" t="n">
-        <v>7245134</v>
+        <v>7245091</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646847</v>
+        <v>122646868</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550746</v>
+        <v>550694</v>
       </c>
       <c r="R41" t="n">
-        <v>7244802</v>
+        <v>7245016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646863</v>
+        <v>122646824</v>
       </c>
       <c r="B42" t="n">
-        <v>94760</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550698</v>
+        <v>550678</v>
       </c>
       <c r="R42" t="n">
-        <v>7244980</v>
+        <v>7244623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646849</v>
+        <v>122647126</v>
       </c>
       <c r="B43" t="n">
-        <v>90940</v>
+        <v>91235</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550779</v>
+        <v>550801</v>
       </c>
       <c r="R43" t="n">
-        <v>7244796</v>
+        <v>7244998</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646856</v>
+        <v>122646874</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>74868</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550759</v>
+        <v>550824</v>
       </c>
       <c r="R44" t="n">
-        <v>7244890</v>
+        <v>7245149</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646865</v>
+        <v>122646821</v>
       </c>
       <c r="B45" t="n">
-        <v>79872</v>
+        <v>74858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550706</v>
+        <v>550670</v>
       </c>
       <c r="R45" t="n">
-        <v>7245002</v>
+        <v>7244542</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646821</v>
+        <v>122646865</v>
       </c>
       <c r="B46" t="n">
-        <v>74858</v>
+        <v>79876</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550670</v>
+        <v>550706</v>
       </c>
       <c r="R46" t="n">
-        <v>7244542</v>
+        <v>7245002</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646846</v>
+        <v>122647137</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>91293</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>2062</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550720</v>
+        <v>550827</v>
       </c>
       <c r="R47" t="n">
-        <v>7244779</v>
+        <v>7245136</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646853</v>
+        <v>122647136</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>91235</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550761</v>
+        <v>550831</v>
       </c>
       <c r="R48" t="n">
-        <v>7244876</v>
+        <v>7245134</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646861</v>
+        <v>122646864</v>
       </c>
       <c r="B15" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550710</v>
+        <v>550696</v>
       </c>
       <c r="R15" t="n">
-        <v>7244974</v>
+        <v>7244978</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646845</v>
+        <v>122646861</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550631</v>
+        <v>550710</v>
       </c>
       <c r="R16" t="n">
-        <v>7244710</v>
+        <v>7244974</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646864</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550696</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7244978</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646851</v>
+        <v>122647138</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550748</v>
+        <v>550832</v>
       </c>
       <c r="R24" t="n">
-        <v>7244855</v>
+        <v>7245128</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3185,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646854</v>
+        <v>122646851</v>
       </c>
       <c r="B25" t="n">
-        <v>94756</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,25 +3197,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550764</v>
+        <v>550748</v>
       </c>
       <c r="R25" t="n">
-        <v>7244897</v>
+        <v>7244855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122647138</v>
+        <v>122646854</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>94756</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550832</v>
+        <v>550764</v>
       </c>
       <c r="R26" t="n">
-        <v>7245128</v>
+        <v>7244897</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646868</v>
+        <v>122646824</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550694</v>
+        <v>550678</v>
       </c>
       <c r="R41" t="n">
-        <v>7245016</v>
+        <v>7244623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646824</v>
+        <v>122647126</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550678</v>
+        <v>550801</v>
       </c>
       <c r="R42" t="n">
-        <v>7244623</v>
+        <v>7244998</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122647126</v>
+        <v>122646874</v>
       </c>
       <c r="B43" t="n">
-        <v>91235</v>
+        <v>74868</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550801</v>
+        <v>550824</v>
       </c>
       <c r="R43" t="n">
-        <v>7244998</v>
+        <v>7245149</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646874</v>
+        <v>122646868</v>
       </c>
       <c r="B44" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550824</v>
+        <v>550694</v>
       </c>
       <c r="R44" t="n">
-        <v>7245149</v>
+        <v>7245016</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646870</v>
+        <v>122646823</v>
       </c>
       <c r="B11" t="n">
-        <v>74858</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550726</v>
+        <v>550677</v>
       </c>
       <c r="R11" t="n">
-        <v>7245050</v>
+        <v>7244586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646852</v>
+        <v>122646872</v>
       </c>
       <c r="B12" t="n">
-        <v>91632</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550744</v>
+        <v>550828</v>
       </c>
       <c r="R12" t="n">
-        <v>7244856</v>
+        <v>7245091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646869</v>
+        <v>122646824</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550688</v>
+        <v>550678</v>
       </c>
       <c r="R13" t="n">
-        <v>7245034</v>
+        <v>7244623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646878</v>
+        <v>122646853</v>
       </c>
       <c r="B14" t="n">
-        <v>97309</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550829</v>
+        <v>550761</v>
       </c>
       <c r="R14" t="n">
-        <v>7245185</v>
+        <v>7244876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646864</v>
+        <v>122646878</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>97309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550696</v>
+        <v>550829</v>
       </c>
       <c r="R15" t="n">
-        <v>7244978</v>
+        <v>7245185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646861</v>
+        <v>122647137</v>
       </c>
       <c r="B16" t="n">
-        <v>74847</v>
+        <v>91293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550710</v>
+        <v>550827</v>
       </c>
       <c r="R16" t="n">
-        <v>7244974</v>
+        <v>7245136</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,7 +2327,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646866</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550706</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7245009</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647146</v>
+        <v>122646868</v>
       </c>
       <c r="B18" t="n">
-        <v>57398</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102110</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550861</v>
+        <v>550694</v>
       </c>
       <c r="R18" t="n">
-        <v>7245193</v>
+        <v>7245016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,17 +2503,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,7 +2528,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2544,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646849</v>
+        <v>122646871</v>
       </c>
       <c r="B19" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550779</v>
+        <v>550784</v>
       </c>
       <c r="R19" t="n">
-        <v>7244796</v>
+        <v>7245041</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647144</v>
+        <v>122646854</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>94756</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,25 +2657,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550854</v>
+        <v>550764</v>
       </c>
       <c r="R20" t="n">
-        <v>7245180</v>
+        <v>7244897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2715,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2740,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2756,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646871</v>
+        <v>122647145</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>88303</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2767,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550784</v>
+        <v>550855</v>
       </c>
       <c r="R21" t="n">
-        <v>7245041</v>
+        <v>7245196</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2821,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,7 +2846,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646853</v>
+        <v>122646865</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2869,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550761</v>
+        <v>550706</v>
       </c>
       <c r="R22" t="n">
-        <v>7244876</v>
+        <v>7245002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646850</v>
+        <v>122646847</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,25 +2975,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550760</v>
+        <v>550746</v>
       </c>
       <c r="R23" t="n">
-        <v>7244829</v>
+        <v>7244802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,11 +3039,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122647138</v>
+        <v>122646848</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>91632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3091,25 +3081,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550832</v>
+        <v>550776</v>
       </c>
       <c r="R24" t="n">
-        <v>7245128</v>
+        <v>7244797</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,12 +3139,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,7 +3164,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3185,7 +3175,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646851</v>
+        <v>122646846</v>
       </c>
       <c r="B25" t="n">
         <v>74863</v>
@@ -3225,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550748</v>
+        <v>550720</v>
       </c>
       <c r="R25" t="n">
-        <v>7244855</v>
+        <v>7244779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646854</v>
+        <v>122646864</v>
       </c>
       <c r="B26" t="n">
-        <v>94756</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550764</v>
+        <v>550696</v>
       </c>
       <c r="R26" t="n">
-        <v>7244897</v>
+        <v>7244978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646856</v>
+        <v>122646851</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3413,21 +3403,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3437,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550759</v>
+        <v>550748</v>
       </c>
       <c r="R27" t="n">
-        <v>7244890</v>
+        <v>7244855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646847</v>
+        <v>122646870</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>74858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3519,21 +3509,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550746</v>
+        <v>550726</v>
       </c>
       <c r="R28" t="n">
-        <v>7244802</v>
+        <v>7245050</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646863</v>
+        <v>122646852</v>
       </c>
       <c r="B29" t="n">
-        <v>94768</v>
+        <v>91632</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3625,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550698</v>
+        <v>550744</v>
       </c>
       <c r="R29" t="n">
-        <v>7244980</v>
+        <v>7244856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122647145</v>
+        <v>122646857</v>
       </c>
       <c r="B30" t="n">
-        <v>88303</v>
+        <v>74868</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3755,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550855</v>
+        <v>550751</v>
       </c>
       <c r="R30" t="n">
-        <v>7245196</v>
+        <v>7244916</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3785,12 +3775,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,7 +3800,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3821,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646846</v>
+        <v>122646845</v>
       </c>
       <c r="B31" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550720</v>
+        <v>550631</v>
       </c>
       <c r="R31" t="n">
-        <v>7244779</v>
+        <v>7244710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4033,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646822</v>
+        <v>122646874</v>
       </c>
       <c r="B33" t="n">
-        <v>96223</v>
+        <v>74868</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4049,21 +4039,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1841</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550659</v>
+        <v>550824</v>
       </c>
       <c r="R33" t="n">
-        <v>7244555</v>
+        <v>7245149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646808</v>
+        <v>122647146</v>
       </c>
       <c r="B34" t="n">
-        <v>57589</v>
+        <v>57398</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4141,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>102110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550651</v>
+        <v>550861</v>
       </c>
       <c r="R34" t="n">
-        <v>7244779</v>
+        <v>7245193</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,12 +4199,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4234,7 +4229,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4245,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646823</v>
+        <v>122647126</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4261,21 +4256,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550677</v>
+        <v>550801</v>
       </c>
       <c r="R35" t="n">
-        <v>7244586</v>
+        <v>7244998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4315,12 +4310,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4340,7 +4335,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4351,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646857</v>
+        <v>122646850</v>
       </c>
       <c r="B36" t="n">
-        <v>74868</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,25 +4358,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1467</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550751</v>
+        <v>550760</v>
       </c>
       <c r="R36" t="n">
-        <v>7244916</v>
+        <v>7244829</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4427,6 +4422,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646873</v>
+        <v>122647144</v>
       </c>
       <c r="B37" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550828</v>
+        <v>550854</v>
       </c>
       <c r="R37" t="n">
-        <v>7245125</v>
+        <v>7245180</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4527,12 +4527,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646866</v>
+        <v>122646873</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4575,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550706</v>
+        <v>550828</v>
       </c>
       <c r="R38" t="n">
-        <v>7245009</v>
+        <v>7245125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646848</v>
+        <v>122646822</v>
       </c>
       <c r="B39" t="n">
-        <v>91632</v>
+        <v>96223</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>1841</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550776</v>
+        <v>550659</v>
       </c>
       <c r="R39" t="n">
-        <v>7244797</v>
+        <v>7244555</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646872</v>
+        <v>122646849</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550828</v>
+        <v>550779</v>
       </c>
       <c r="R40" t="n">
-        <v>7245091</v>
+        <v>7244796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646824</v>
+        <v>122647138</v>
       </c>
       <c r="B41" t="n">
         <v>90944</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550678</v>
+        <v>550832</v>
       </c>
       <c r="R41" t="n">
-        <v>7244623</v>
+        <v>7245128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4987,7 +4987,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122647126</v>
+        <v>122647136</v>
       </c>
       <c r="B42" t="n">
         <v>91235</v>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550801</v>
+        <v>550831</v>
       </c>
       <c r="R42" t="n">
-        <v>7244998</v>
+        <v>7245134</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646874</v>
+        <v>122646869</v>
       </c>
       <c r="B43" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550824</v>
+        <v>550688</v>
       </c>
       <c r="R43" t="n">
-        <v>7245149</v>
+        <v>7245034</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646868</v>
+        <v>122646861</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>74847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5211,25 +5211,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550694</v>
+        <v>550710</v>
       </c>
       <c r="R44" t="n">
-        <v>7245016</v>
+        <v>7244974</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646821</v>
+        <v>122646856</v>
       </c>
       <c r="B45" t="n">
-        <v>74858</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550670</v>
+        <v>550759</v>
       </c>
       <c r="R45" t="n">
-        <v>7244542</v>
+        <v>7244890</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646865</v>
+        <v>122646808</v>
       </c>
       <c r="B46" t="n">
-        <v>79876</v>
+        <v>57589</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550706</v>
+        <v>550651</v>
       </c>
       <c r="R46" t="n">
-        <v>7245002</v>
+        <v>7244779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122647137</v>
+        <v>122646821</v>
       </c>
       <c r="B47" t="n">
-        <v>91293</v>
+        <v>74858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2062</v>
+        <v>310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550827</v>
+        <v>550670</v>
       </c>
       <c r="R47" t="n">
-        <v>7245136</v>
+        <v>7244542</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122647136</v>
+        <v>122646863</v>
       </c>
       <c r="B48" t="n">
-        <v>91235</v>
+        <v>94768</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550831</v>
+        <v>550698</v>
       </c>
       <c r="R48" t="n">
-        <v>7245134</v>
+        <v>7244980</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646823</v>
+        <v>122646865</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550677</v>
+        <v>550706</v>
       </c>
       <c r="R11" t="n">
-        <v>7244586</v>
+        <v>7245002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646872</v>
+        <v>122646852</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>91632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550828</v>
+        <v>550744</v>
       </c>
       <c r="R12" t="n">
-        <v>7245091</v>
+        <v>7244856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646824</v>
+        <v>122646821</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>74858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550678</v>
+        <v>550670</v>
       </c>
       <c r="R13" t="n">
-        <v>7244623</v>
+        <v>7244542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646853</v>
+        <v>122646823</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550761</v>
+        <v>550677</v>
       </c>
       <c r="R14" t="n">
-        <v>7244876</v>
+        <v>7244586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646878</v>
+        <v>122646873</v>
       </c>
       <c r="B15" t="n">
-        <v>97309</v>
+        <v>57589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550829</v>
+        <v>550828</v>
       </c>
       <c r="R15" t="n">
-        <v>7245185</v>
+        <v>7245125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647137</v>
+        <v>122647138</v>
       </c>
       <c r="B16" t="n">
-        <v>91293</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550827</v>
+        <v>550832</v>
       </c>
       <c r="R16" t="n">
-        <v>7245136</v>
+        <v>7245128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646866</v>
+        <v>122646846</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550706</v>
+        <v>550720</v>
       </c>
       <c r="R17" t="n">
-        <v>7245009</v>
+        <v>7244779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646868</v>
+        <v>122646847</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550694</v>
+        <v>550746</v>
       </c>
       <c r="R18" t="n">
-        <v>7245016</v>
+        <v>7244802</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646871</v>
+        <v>122647137</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>91293</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550784</v>
+        <v>550827</v>
       </c>
       <c r="R19" t="n">
-        <v>7245041</v>
+        <v>7245136</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646854</v>
+        <v>122646848</v>
       </c>
       <c r="B20" t="n">
-        <v>94756</v>
+        <v>91632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550764</v>
+        <v>550776</v>
       </c>
       <c r="R20" t="n">
-        <v>7244897</v>
+        <v>7244797</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647145</v>
+        <v>122646868</v>
       </c>
       <c r="B21" t="n">
-        <v>88303</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550855</v>
+        <v>550694</v>
       </c>
       <c r="R21" t="n">
-        <v>7245196</v>
+        <v>7245016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2857,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646865</v>
+        <v>122646855</v>
       </c>
       <c r="B22" t="n">
-        <v>79876</v>
+        <v>94758</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,21 +2873,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550706</v>
+        <v>550770</v>
       </c>
       <c r="R22" t="n">
-        <v>7245002</v>
+        <v>7244875</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646847</v>
+        <v>122646849</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550746</v>
+        <v>550779</v>
       </c>
       <c r="R23" t="n">
-        <v>7244802</v>
+        <v>7244796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646848</v>
+        <v>122646861</v>
       </c>
       <c r="B24" t="n">
-        <v>91632</v>
+        <v>74847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,21 +3085,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550776</v>
+        <v>550710</v>
       </c>
       <c r="R24" t="n">
-        <v>7244797</v>
+        <v>7244974</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646846</v>
+        <v>122646871</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550720</v>
+        <v>550784</v>
       </c>
       <c r="R25" t="n">
-        <v>7244779</v>
+        <v>7245041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646864</v>
+        <v>122646863</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>94770</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550696</v>
+        <v>550698</v>
       </c>
       <c r="R26" t="n">
-        <v>7244978</v>
+        <v>7244980</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646851</v>
+        <v>122646864</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550748</v>
+        <v>550696</v>
       </c>
       <c r="R27" t="n">
-        <v>7244855</v>
+        <v>7244978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646870</v>
+        <v>122646824</v>
       </c>
       <c r="B28" t="n">
-        <v>74858</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550726</v>
+        <v>550678</v>
       </c>
       <c r="R28" t="n">
-        <v>7245050</v>
+        <v>7244623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646852</v>
+        <v>122646857</v>
       </c>
       <c r="B29" t="n">
-        <v>91632</v>
+        <v>74868</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3611,25 +3611,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550744</v>
+        <v>550751</v>
       </c>
       <c r="R29" t="n">
-        <v>7244856</v>
+        <v>7244916</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646857</v>
+        <v>122646845</v>
       </c>
       <c r="B30" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550751</v>
+        <v>550631</v>
       </c>
       <c r="R30" t="n">
-        <v>7244916</v>
+        <v>7244710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646845</v>
+        <v>122646853</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550631</v>
+        <v>550761</v>
       </c>
       <c r="R31" t="n">
-        <v>7244710</v>
+        <v>7244876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646855</v>
+        <v>122646869</v>
       </c>
       <c r="B32" t="n">
-        <v>94756</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,25 +3929,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550770</v>
+        <v>550688</v>
       </c>
       <c r="R32" t="n">
-        <v>7244875</v>
+        <v>7245034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646874</v>
+        <v>122647145</v>
       </c>
       <c r="B33" t="n">
-        <v>74868</v>
+        <v>88303</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550824</v>
+        <v>550855</v>
       </c>
       <c r="R33" t="n">
-        <v>7245149</v>
+        <v>7245196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122647146</v>
+        <v>122646850</v>
       </c>
       <c r="B34" t="n">
-        <v>57398</v>
+        <v>56688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4141,25 +4141,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102110</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550861</v>
+        <v>550760</v>
       </c>
       <c r="R34" t="n">
-        <v>7245193</v>
+        <v>7244829</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122647126</v>
+        <v>122646874</v>
       </c>
       <c r="B35" t="n">
-        <v>91235</v>
+        <v>74868</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550801</v>
+        <v>550824</v>
       </c>
       <c r="R35" t="n">
-        <v>7244998</v>
+        <v>7245149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4346,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646850</v>
+        <v>122647136</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>91235</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4358,25 +4358,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550760</v>
+        <v>550831</v>
       </c>
       <c r="R36" t="n">
-        <v>7244829</v>
+        <v>7245134</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4416,17 +4416,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4446,7 +4441,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4457,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122647144</v>
+        <v>122646872</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,21 +4468,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550854</v>
+        <v>550828</v>
       </c>
       <c r="R37" t="n">
-        <v>7245180</v>
+        <v>7245091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4527,12 +4522,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4552,7 +4547,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4563,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646873</v>
+        <v>122647126</v>
       </c>
       <c r="B38" t="n">
-        <v>57589</v>
+        <v>91235</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,25 +4570,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550828</v>
+        <v>550801</v>
       </c>
       <c r="R38" t="n">
-        <v>7245125</v>
+        <v>7244998</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4633,12 +4628,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,7 +4653,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4669,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646822</v>
+        <v>122646866</v>
       </c>
       <c r="B39" t="n">
-        <v>96223</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,21 +4680,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550659</v>
+        <v>550706</v>
       </c>
       <c r="R39" t="n">
-        <v>7244555</v>
+        <v>7245009</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646849</v>
+        <v>122646878</v>
       </c>
       <c r="B40" t="n">
-        <v>90944</v>
+        <v>97311</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550779</v>
+        <v>550829</v>
       </c>
       <c r="R40" t="n">
-        <v>7244796</v>
+        <v>7245185</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122647138</v>
+        <v>122647144</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4892,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550832</v>
+        <v>550854</v>
       </c>
       <c r="R41" t="n">
-        <v>7245128</v>
+        <v>7245180</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122647136</v>
+        <v>122646856</v>
       </c>
       <c r="B42" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +4998,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550831</v>
+        <v>550759</v>
       </c>
       <c r="R42" t="n">
-        <v>7245134</v>
+        <v>7244890</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,12 +5052,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5077,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5093,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646869</v>
+        <v>122646822</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>96225</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1841</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550688</v>
+        <v>550659</v>
       </c>
       <c r="R43" t="n">
-        <v>7245034</v>
+        <v>7244555</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646861</v>
+        <v>122647146</v>
       </c>
       <c r="B44" t="n">
-        <v>74847</v>
+        <v>57398</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5211,25 +5206,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>102110</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550710</v>
+        <v>550861</v>
       </c>
       <c r="R44" t="n">
-        <v>7244974</v>
+        <v>7245193</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5269,12 +5264,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646856</v>
+        <v>122646808</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550759</v>
+        <v>550651</v>
       </c>
       <c r="R45" t="n">
-        <v>7244890</v>
+        <v>7244779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646808</v>
+        <v>122646854</v>
       </c>
       <c r="B46" t="n">
-        <v>57589</v>
+        <v>94758</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>2809</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550651</v>
+        <v>550764</v>
       </c>
       <c r="R46" t="n">
-        <v>7244779</v>
+        <v>7244897</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646821</v>
+        <v>122646851</v>
       </c>
       <c r="B47" t="n">
-        <v>74858</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550670</v>
+        <v>550748</v>
       </c>
       <c r="R47" t="n">
-        <v>7244542</v>
+        <v>7244855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646863</v>
+        <v>122646870</v>
       </c>
       <c r="B48" t="n">
-        <v>94768</v>
+        <v>74858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2813</v>
+        <v>310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550698</v>
+        <v>550726</v>
       </c>
       <c r="R48" t="n">
-        <v>7244980</v>
+        <v>7245050</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646873</v>
+        <v>122647138</v>
       </c>
       <c r="B15" t="n">
-        <v>57589</v>
+        <v>90944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550828</v>
+        <v>550832</v>
       </c>
       <c r="R15" t="n">
-        <v>7245125</v>
+        <v>7245128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647138</v>
+        <v>122646846</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550832</v>
+        <v>550720</v>
       </c>
       <c r="R16" t="n">
-        <v>7245128</v>
+        <v>7244779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646846</v>
+        <v>122646873</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550720</v>
+        <v>550828</v>
       </c>
       <c r="R17" t="n">
-        <v>7244779</v>
+        <v>7245125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646864</v>
+        <v>122646824</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550696</v>
+        <v>550678</v>
       </c>
       <c r="R27" t="n">
-        <v>7244978</v>
+        <v>7244623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646824</v>
+        <v>122646857</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>74868</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550678</v>
+        <v>550751</v>
       </c>
       <c r="R28" t="n">
-        <v>7244623</v>
+        <v>7244916</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646857</v>
+        <v>122646864</v>
       </c>
       <c r="B29" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550751</v>
+        <v>550696</v>
       </c>
       <c r="R29" t="n">
-        <v>7244916</v>
+        <v>7244978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646869</v>
+        <v>122647145</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>88303</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550688</v>
+        <v>550855</v>
       </c>
       <c r="R32" t="n">
-        <v>7245034</v>
+        <v>7245196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122647145</v>
+        <v>122646869</v>
       </c>
       <c r="B33" t="n">
-        <v>88303</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550855</v>
+        <v>550688</v>
       </c>
       <c r="R33" t="n">
-        <v>7245196</v>
+        <v>7245034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -3387,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646824</v>
+        <v>122646864</v>
       </c>
       <c r="B27" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550678</v>
+        <v>550696</v>
       </c>
       <c r="R27" t="n">
-        <v>7244623</v>
+        <v>7244978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646857</v>
+        <v>122646824</v>
       </c>
       <c r="B28" t="n">
-        <v>74868</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550751</v>
+        <v>550678</v>
       </c>
       <c r="R28" t="n">
-        <v>7244916</v>
+        <v>7244623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646864</v>
+        <v>122646857</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550696</v>
+        <v>550751</v>
       </c>
       <c r="R29" t="n">
-        <v>7244978</v>
+        <v>7244916</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646865</v>
+        <v>122646846</v>
       </c>
       <c r="B11" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550706</v>
+        <v>550720</v>
       </c>
       <c r="R11" t="n">
-        <v>7245002</v>
+        <v>7244779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646852</v>
+        <v>122646821</v>
       </c>
       <c r="B12" t="n">
-        <v>91632</v>
+        <v>74858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550744</v>
+        <v>550670</v>
       </c>
       <c r="R12" t="n">
-        <v>7244856</v>
+        <v>7244542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646821</v>
+        <v>122646870</v>
       </c>
       <c r="B13" t="n">
         <v>74858</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550670</v>
+        <v>550726</v>
       </c>
       <c r="R13" t="n">
-        <v>7244542</v>
+        <v>7245050</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646823</v>
+        <v>122646854</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>94758</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550677</v>
+        <v>550764</v>
       </c>
       <c r="R14" t="n">
-        <v>7244586</v>
+        <v>7244897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647138</v>
+        <v>122646847</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550832</v>
+        <v>550746</v>
       </c>
       <c r="R15" t="n">
-        <v>7245128</v>
+        <v>7244802</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646846</v>
+        <v>122647136</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550720</v>
+        <v>550831</v>
       </c>
       <c r="R16" t="n">
-        <v>7244779</v>
+        <v>7245134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646873</v>
+        <v>122646871</v>
       </c>
       <c r="B17" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550828</v>
+        <v>550784</v>
       </c>
       <c r="R17" t="n">
-        <v>7245125</v>
+        <v>7245041</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646847</v>
+        <v>122646845</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550746</v>
+        <v>550631</v>
       </c>
       <c r="R18" t="n">
-        <v>7244802</v>
+        <v>7244710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647137</v>
+        <v>122646823</v>
       </c>
       <c r="B19" t="n">
-        <v>91293</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550827</v>
+        <v>550677</v>
       </c>
       <c r="R19" t="n">
-        <v>7245136</v>
+        <v>7244586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646848</v>
+        <v>122646868</v>
       </c>
       <c r="B20" t="n">
-        <v>91632</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,25 +2657,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550776</v>
+        <v>550694</v>
       </c>
       <c r="R20" t="n">
-        <v>7244797</v>
+        <v>7245016</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646868</v>
+        <v>122646848</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>91632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,25 +2763,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550694</v>
+        <v>550776</v>
       </c>
       <c r="R21" t="n">
-        <v>7245016</v>
+        <v>7244797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646855</v>
+        <v>122646852</v>
       </c>
       <c r="B22" t="n">
-        <v>94758</v>
+        <v>91632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,21 +2873,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550770</v>
+        <v>550744</v>
       </c>
       <c r="R22" t="n">
-        <v>7244875</v>
+        <v>7244856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646849</v>
+        <v>122646864</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550779</v>
+        <v>550696</v>
       </c>
       <c r="R23" t="n">
-        <v>7244796</v>
+        <v>7244978</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646861</v>
+        <v>122646855</v>
       </c>
       <c r="B24" t="n">
-        <v>74847</v>
+        <v>94758</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,21 +3085,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550710</v>
+        <v>550770</v>
       </c>
       <c r="R24" t="n">
-        <v>7244974</v>
+        <v>7244875</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646871</v>
+        <v>122646857</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550784</v>
+        <v>550751</v>
       </c>
       <c r="R25" t="n">
-        <v>7245041</v>
+        <v>7244916</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646863</v>
+        <v>122646866</v>
       </c>
       <c r="B26" t="n">
-        <v>94770</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550698</v>
+        <v>550706</v>
       </c>
       <c r="R26" t="n">
-        <v>7244980</v>
+        <v>7245009</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646864</v>
+        <v>122647145</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>88303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550696</v>
+        <v>550855</v>
       </c>
       <c r="R27" t="n">
-        <v>7244978</v>
+        <v>7245196</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3493,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646824</v>
+        <v>122646878</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>97311</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550678</v>
+        <v>550829</v>
       </c>
       <c r="R28" t="n">
-        <v>7244623</v>
+        <v>7245185</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646857</v>
+        <v>122646853</v>
       </c>
       <c r="B29" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550751</v>
+        <v>550761</v>
       </c>
       <c r="R29" t="n">
-        <v>7244916</v>
+        <v>7244876</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646845</v>
+        <v>122647126</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550631</v>
+        <v>550801</v>
       </c>
       <c r="R30" t="n">
-        <v>7244710</v>
+        <v>7244998</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646853</v>
+        <v>122646863</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>94770</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,25 +3823,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550761</v>
+        <v>550698</v>
       </c>
       <c r="R31" t="n">
-        <v>7244876</v>
+        <v>7244980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122647145</v>
+        <v>122646808</v>
       </c>
       <c r="B32" t="n">
-        <v>88303</v>
+        <v>57589</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,25 +3929,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550855</v>
+        <v>550651</v>
       </c>
       <c r="R32" t="n">
-        <v>7245196</v>
+        <v>7244779</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646869</v>
+        <v>122646849</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,21 +4039,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550688</v>
+        <v>550779</v>
       </c>
       <c r="R33" t="n">
-        <v>7245034</v>
+        <v>7244796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646850</v>
+        <v>122647146</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>57398</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4141,25 +4141,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>102110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550760</v>
+        <v>550861</v>
       </c>
       <c r="R34" t="n">
-        <v>7244829</v>
+        <v>7245193</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Uppflygande</t>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646874</v>
+        <v>122646869</v>
       </c>
       <c r="B35" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550824</v>
+        <v>550688</v>
       </c>
       <c r="R35" t="n">
-        <v>7245149</v>
+        <v>7245034</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4346,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122647136</v>
+        <v>122647144</v>
       </c>
       <c r="B36" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4362,21 +4362,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550831</v>
+        <v>550854</v>
       </c>
       <c r="R36" t="n">
-        <v>7245134</v>
+        <v>7245180</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646872</v>
+        <v>122646851</v>
       </c>
       <c r="B37" t="n">
         <v>74863</v>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550828</v>
+        <v>550748</v>
       </c>
       <c r="R37" t="n">
-        <v>7245091</v>
+        <v>7244855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122647126</v>
+        <v>122647138</v>
       </c>
       <c r="B38" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550801</v>
+        <v>550832</v>
       </c>
       <c r="R38" t="n">
-        <v>7244998</v>
+        <v>7245128</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646866</v>
+        <v>122646850</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550706</v>
+        <v>550760</v>
       </c>
       <c r="R39" t="n">
-        <v>7245009</v>
+        <v>7244829</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,6 +4740,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646878</v>
+        <v>122646865</v>
       </c>
       <c r="B40" t="n">
-        <v>97311</v>
+        <v>79876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4786,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550829</v>
+        <v>550706</v>
       </c>
       <c r="R40" t="n">
-        <v>7245185</v>
+        <v>7245002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4876,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122647144</v>
+        <v>122646874</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4916,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550854</v>
+        <v>550824</v>
       </c>
       <c r="R41" t="n">
-        <v>7245180</v>
+        <v>7245149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,12 +4951,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4971,7 +4976,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4982,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646856</v>
+        <v>122646873</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4994,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5022,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550759</v>
+        <v>550828</v>
       </c>
       <c r="R42" t="n">
-        <v>7244890</v>
+        <v>7245125</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646822</v>
+        <v>122646824</v>
       </c>
       <c r="B43" t="n">
-        <v>96225</v>
+        <v>90944</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1841</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550659</v>
+        <v>550678</v>
       </c>
       <c r="R43" t="n">
-        <v>7244555</v>
+        <v>7244623</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122647146</v>
+        <v>122646856</v>
       </c>
       <c r="B44" t="n">
-        <v>57398</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5210,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102110</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550861</v>
+        <v>550759</v>
       </c>
       <c r="R44" t="n">
-        <v>7245193</v>
+        <v>7244890</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,17 +5269,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646808</v>
+        <v>122647137</v>
       </c>
       <c r="B45" t="n">
-        <v>57589</v>
+        <v>91293</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>2062</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550651</v>
+        <v>550827</v>
       </c>
       <c r="R45" t="n">
-        <v>7244779</v>
+        <v>7245136</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646854</v>
+        <v>122646861</v>
       </c>
       <c r="B46" t="n">
-        <v>94758</v>
+        <v>74847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550764</v>
+        <v>550710</v>
       </c>
       <c r="R46" t="n">
-        <v>7244897</v>
+        <v>7244974</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646851</v>
+        <v>122646822</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>96225</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1841</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550748</v>
+        <v>550659</v>
       </c>
       <c r="R47" t="n">
-        <v>7244855</v>
+        <v>7244555</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646870</v>
+        <v>122646872</v>
       </c>
       <c r="B48" t="n">
-        <v>74858</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550726</v>
+        <v>550828</v>
       </c>
       <c r="R48" t="n">
-        <v>7245050</v>
+        <v>7245091</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646846</v>
+        <v>122646854</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>94758</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550720</v>
+        <v>550764</v>
       </c>
       <c r="R11" t="n">
-        <v>7244779</v>
+        <v>7244897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646821</v>
+        <v>122646846</v>
       </c>
       <c r="B12" t="n">
-        <v>74858</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>310</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550670</v>
+        <v>550720</v>
       </c>
       <c r="R12" t="n">
-        <v>7244542</v>
+        <v>7244779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646870</v>
+        <v>122646821</v>
       </c>
       <c r="B13" t="n">
         <v>74858</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550726</v>
+        <v>550670</v>
       </c>
       <c r="R13" t="n">
-        <v>7245050</v>
+        <v>7244542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646854</v>
+        <v>122646870</v>
       </c>
       <c r="B14" t="n">
-        <v>94758</v>
+        <v>74858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550764</v>
+        <v>550726</v>
       </c>
       <c r="R14" t="n">
-        <v>7244897</v>
+        <v>7245050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647136</v>
+        <v>122646871</v>
       </c>
       <c r="B16" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550831</v>
+        <v>550784</v>
       </c>
       <c r="R16" t="n">
-        <v>7245134</v>
+        <v>7245041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,7 +2327,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646871</v>
+        <v>122646845</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550784</v>
+        <v>550631</v>
       </c>
       <c r="R17" t="n">
-        <v>7245041</v>
+        <v>7244710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646845</v>
+        <v>122646823</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550631</v>
+        <v>550677</v>
       </c>
       <c r="R18" t="n">
-        <v>7244710</v>
+        <v>7244586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646823</v>
+        <v>122647136</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550677</v>
+        <v>550831</v>
       </c>
       <c r="R19" t="n">
-        <v>7244586</v>
+        <v>7245134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646850</v>
+        <v>122646865</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>79876</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550760</v>
+        <v>550706</v>
       </c>
       <c r="R39" t="n">
-        <v>7244829</v>
+        <v>7245002</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,11 +4740,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646865</v>
+        <v>122646850</v>
       </c>
       <c r="B40" t="n">
-        <v>79876</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4786,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550706</v>
+        <v>550760</v>
       </c>
       <c r="R40" t="n">
-        <v>7245002</v>
+        <v>7244829</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4851,6 +4846,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646824</v>
+        <v>122646856</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550678</v>
+        <v>550759</v>
       </c>
       <c r="R43" t="n">
-        <v>7244623</v>
+        <v>7244890</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646856</v>
+        <v>122646824</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550759</v>
+        <v>550678</v>
       </c>
       <c r="R44" t="n">
-        <v>7244890</v>
+        <v>7244623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646854</v>
+        <v>122646846</v>
       </c>
       <c r="B11" t="n">
-        <v>94758</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550764</v>
+        <v>550720</v>
       </c>
       <c r="R11" t="n">
-        <v>7244897</v>
+        <v>7244779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646846</v>
+        <v>122646821</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>74858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550720</v>
+        <v>550670</v>
       </c>
       <c r="R12" t="n">
-        <v>7244779</v>
+        <v>7244542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646821</v>
+        <v>122646870</v>
       </c>
       <c r="B13" t="n">
         <v>74858</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550670</v>
+        <v>550726</v>
       </c>
       <c r="R13" t="n">
-        <v>7244542</v>
+        <v>7245050</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646870</v>
+        <v>122646854</v>
       </c>
       <c r="B14" t="n">
-        <v>74858</v>
+        <v>94758</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>310</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550726</v>
+        <v>550764</v>
       </c>
       <c r="R14" t="n">
-        <v>7245050</v>
+        <v>7244897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646871</v>
+        <v>122647136</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550784</v>
+        <v>550831</v>
       </c>
       <c r="R16" t="n">
-        <v>7245041</v>
+        <v>7245134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,7 +2327,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646845</v>
+        <v>122646871</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550631</v>
+        <v>550784</v>
       </c>
       <c r="R17" t="n">
-        <v>7244710</v>
+        <v>7245041</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646823</v>
+        <v>122646845</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550677</v>
+        <v>550631</v>
       </c>
       <c r="R18" t="n">
-        <v>7244586</v>
+        <v>7244710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647136</v>
+        <v>122646823</v>
       </c>
       <c r="B19" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550831</v>
+        <v>550677</v>
       </c>
       <c r="R19" t="n">
-        <v>7245134</v>
+        <v>7244586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646865</v>
+        <v>122646850</v>
       </c>
       <c r="B39" t="n">
-        <v>79876</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550706</v>
+        <v>550760</v>
       </c>
       <c r="R39" t="n">
-        <v>7245002</v>
+        <v>7244829</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,6 +4740,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646850</v>
+        <v>122646865</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>79876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4786,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4810,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550760</v>
+        <v>550706</v>
       </c>
       <c r="R40" t="n">
-        <v>7244829</v>
+        <v>7245002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4846,11 +4851,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646846</v>
+        <v>122646872</v>
       </c>
       <c r="B11" t="n">
         <v>74863</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550720</v>
+        <v>550828</v>
       </c>
       <c r="R11" t="n">
-        <v>7244779</v>
+        <v>7245091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646821</v>
+        <v>122646852</v>
       </c>
       <c r="B12" t="n">
-        <v>74858</v>
+        <v>91640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>310</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550670</v>
+        <v>550744</v>
       </c>
       <c r="R12" t="n">
-        <v>7244542</v>
+        <v>7244856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646870</v>
+        <v>122646850</v>
       </c>
       <c r="B13" t="n">
-        <v>74858</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>310</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550726</v>
+        <v>550760</v>
       </c>
       <c r="R13" t="n">
-        <v>7245050</v>
+        <v>7244829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,6 +1979,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646854</v>
+        <v>122646866</v>
       </c>
       <c r="B14" t="n">
-        <v>94758</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2026,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550764</v>
+        <v>550706</v>
       </c>
       <c r="R14" t="n">
-        <v>7244897</v>
+        <v>7245009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646847</v>
+        <v>122646808</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2132,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550746</v>
+        <v>550651</v>
       </c>
       <c r="R15" t="n">
-        <v>7244802</v>
+        <v>7244779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647136</v>
+        <v>122646878</v>
       </c>
       <c r="B16" t="n">
-        <v>91235</v>
+        <v>97319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,25 +2238,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550831</v>
+        <v>550829</v>
       </c>
       <c r="R16" t="n">
-        <v>7245134</v>
+        <v>7245185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,12 +2296,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2321,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2327,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646871</v>
+        <v>122646865</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550784</v>
+        <v>550706</v>
       </c>
       <c r="R17" t="n">
-        <v>7245041</v>
+        <v>7245002</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2438,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646845</v>
+        <v>122646856</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2473,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550631</v>
+        <v>550759</v>
       </c>
       <c r="R18" t="n">
-        <v>7244710</v>
+        <v>7244890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646823</v>
+        <v>122646861</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550677</v>
+        <v>550710</v>
       </c>
       <c r="R19" t="n">
-        <v>7244586</v>
+        <v>7244974</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646868</v>
+        <v>122646845</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2685,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550694</v>
+        <v>550631</v>
       </c>
       <c r="R20" t="n">
-        <v>7245016</v>
+        <v>7244710</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646848</v>
+        <v>122647146</v>
       </c>
       <c r="B21" t="n">
-        <v>91632</v>
+        <v>57398</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,25 +2768,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>102110</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2791,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550776</v>
+        <v>550861</v>
       </c>
       <c r="R21" t="n">
-        <v>7244797</v>
+        <v>7245193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,12 +2826,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2856,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2857,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646852</v>
+        <v>122646863</v>
       </c>
       <c r="B22" t="n">
-        <v>91632</v>
+        <v>94778</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,21 +2883,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>2813</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2897,10 +2907,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550744</v>
+        <v>550698</v>
       </c>
       <c r="R22" t="n">
-        <v>7244856</v>
+        <v>7244980</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2963,10 +2973,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646864</v>
+        <v>122646849</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,21 +2989,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3013,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550696</v>
+        <v>550779</v>
       </c>
       <c r="R23" t="n">
-        <v>7244978</v>
+        <v>7244796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646855</v>
+        <v>122646853</v>
       </c>
       <c r="B24" t="n">
-        <v>94758</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,25 +3091,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3109,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550770</v>
+        <v>550761</v>
       </c>
       <c r="R24" t="n">
-        <v>7244875</v>
+        <v>7244876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646857</v>
+        <v>122647145</v>
       </c>
       <c r="B25" t="n">
-        <v>74868</v>
+        <v>88303</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,21 +3201,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550751</v>
+        <v>550855</v>
       </c>
       <c r="R25" t="n">
-        <v>7244916</v>
+        <v>7245196</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3245,12 +3255,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3270,7 +3280,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3281,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646866</v>
+        <v>122646854</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>94766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3321,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550706</v>
+        <v>550764</v>
       </c>
       <c r="R26" t="n">
-        <v>7245009</v>
+        <v>7244897</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122647145</v>
+        <v>122646869</v>
       </c>
       <c r="B27" t="n">
-        <v>88303</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3413,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550855</v>
+        <v>550688</v>
       </c>
       <c r="R27" t="n">
-        <v>7245196</v>
+        <v>7245034</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,12 +3467,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,7 +3492,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3493,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646878</v>
+        <v>122647144</v>
       </c>
       <c r="B28" t="n">
-        <v>97311</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3505,25 +3515,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550829</v>
+        <v>550854</v>
       </c>
       <c r="R28" t="n">
-        <v>7245185</v>
+        <v>7245180</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,12 +3573,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3588,7 +3598,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3599,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646853</v>
+        <v>122646851</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,21 +3625,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550761</v>
+        <v>550748</v>
       </c>
       <c r="R29" t="n">
-        <v>7244876</v>
+        <v>7244855</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122647126</v>
+        <v>122646855</v>
       </c>
       <c r="B30" t="n">
-        <v>91235</v>
+        <v>94766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3717,25 +3727,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550801</v>
+        <v>550770</v>
       </c>
       <c r="R30" t="n">
-        <v>7244998</v>
+        <v>7244875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,12 +3785,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,7 +3810,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3811,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646863</v>
+        <v>122647137</v>
       </c>
       <c r="B31" t="n">
-        <v>94770</v>
+        <v>91301</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550698</v>
+        <v>550827</v>
       </c>
       <c r="R31" t="n">
-        <v>7244980</v>
+        <v>7245136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3881,12 +3891,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,7 +3916,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3917,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646808</v>
+        <v>122646873</v>
       </c>
       <c r="B32" t="n">
         <v>57589</v>
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550651</v>
+        <v>550828</v>
       </c>
       <c r="R32" t="n">
-        <v>7244779</v>
+        <v>7245125</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646849</v>
+        <v>122646848</v>
       </c>
       <c r="B33" t="n">
-        <v>90944</v>
+        <v>91640</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4063,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550779</v>
+        <v>550776</v>
       </c>
       <c r="R33" t="n">
-        <v>7244796</v>
+        <v>7244797</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122647146</v>
+        <v>122646822</v>
       </c>
       <c r="B34" t="n">
-        <v>57398</v>
+        <v>96233</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4145,21 +4155,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102110</v>
+        <v>1841</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4169,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550861</v>
+        <v>550659</v>
       </c>
       <c r="R34" t="n">
-        <v>7245193</v>
+        <v>7244555</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,17 +4209,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4234,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4240,7 +4245,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646869</v>
+        <v>122646846</v>
       </c>
       <c r="B35" t="n">
         <v>74863</v>
@@ -4280,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550688</v>
+        <v>550720</v>
       </c>
       <c r="R35" t="n">
-        <v>7245034</v>
+        <v>7244779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4346,7 +4351,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122647144</v>
+        <v>122646864</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550854</v>
+        <v>550696</v>
       </c>
       <c r="R36" t="n">
-        <v>7245180</v>
+        <v>7244978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4416,12 +4421,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4441,7 +4446,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4452,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646851</v>
+        <v>122646870</v>
       </c>
       <c r="B37" t="n">
-        <v>74863</v>
+        <v>74858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4468,21 +4473,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4492,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550748</v>
+        <v>550726</v>
       </c>
       <c r="R37" t="n">
-        <v>7244855</v>
+        <v>7245050</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122647138</v>
+        <v>122646874</v>
       </c>
       <c r="B38" t="n">
-        <v>90944</v>
+        <v>74868</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4574,21 +4579,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550832</v>
+        <v>550824</v>
       </c>
       <c r="R38" t="n">
-        <v>7245128</v>
+        <v>7245149</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,12 +4633,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,7 +4658,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4664,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646850</v>
+        <v>122647126</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>91243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4676,25 +4681,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4704,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550760</v>
+        <v>550801</v>
       </c>
       <c r="R39" t="n">
-        <v>7244829</v>
+        <v>7244998</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4734,17 +4739,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646865</v>
+        <v>122646857</v>
       </c>
       <c r="B40" t="n">
-        <v>79876</v>
+        <v>74868</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4787,25 +4787,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550706</v>
+        <v>550751</v>
       </c>
       <c r="R40" t="n">
-        <v>7245002</v>
+        <v>7244916</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646874</v>
+        <v>122646847</v>
       </c>
       <c r="B41" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550824</v>
+        <v>550746</v>
       </c>
       <c r="R41" t="n">
-        <v>7245149</v>
+        <v>7244802</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646873</v>
+        <v>122646824</v>
       </c>
       <c r="B42" t="n">
-        <v>57589</v>
+        <v>90952</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550828</v>
+        <v>550678</v>
       </c>
       <c r="R42" t="n">
-        <v>7245125</v>
+        <v>7244623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646856</v>
+        <v>122647136</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550759</v>
+        <v>550831</v>
       </c>
       <c r="R43" t="n">
-        <v>7244890</v>
+        <v>7245134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646824</v>
+        <v>122646823</v>
       </c>
       <c r="B44" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550678</v>
+        <v>550677</v>
       </c>
       <c r="R44" t="n">
-        <v>7244623</v>
+        <v>7244586</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122647137</v>
+        <v>122646868</v>
       </c>
       <c r="B45" t="n">
-        <v>91293</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550827</v>
+        <v>550694</v>
       </c>
       <c r="R45" t="n">
-        <v>7245136</v>
+        <v>7245016</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646861</v>
+        <v>122646821</v>
       </c>
       <c r="B46" t="n">
-        <v>74847</v>
+        <v>74858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550710</v>
+        <v>550670</v>
       </c>
       <c r="R46" t="n">
-        <v>7244974</v>
+        <v>7244542</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646822</v>
+        <v>122647138</v>
       </c>
       <c r="B47" t="n">
-        <v>96225</v>
+        <v>90952</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1841</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550659</v>
+        <v>550832</v>
       </c>
       <c r="R47" t="n">
-        <v>7244555</v>
+        <v>7245128</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646872</v>
+        <v>122646871</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550828</v>
+        <v>550784</v>
       </c>
       <c r="R48" t="n">
-        <v>7245091</v>
+        <v>7245041</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646845</v>
+        <v>122647146</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57398</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550631</v>
+        <v>550861</v>
       </c>
       <c r="R20" t="n">
-        <v>7244710</v>
+        <v>7245193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,12 +2720,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2750,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2756,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647146</v>
+        <v>122646845</v>
       </c>
       <c r="B21" t="n">
-        <v>57398</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102110</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550861</v>
+        <v>550631</v>
       </c>
       <c r="R21" t="n">
-        <v>7245193</v>
+        <v>7244710</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,17 +2831,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3185,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122647145</v>
+        <v>122646854</v>
       </c>
       <c r="B25" t="n">
-        <v>88303</v>
+        <v>94766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,25 +3197,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550855</v>
+        <v>550764</v>
       </c>
       <c r="R25" t="n">
-        <v>7245196</v>
+        <v>7244897</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,12 +3255,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3291,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646854</v>
+        <v>122647145</v>
       </c>
       <c r="B26" t="n">
-        <v>94766</v>
+        <v>88303</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550764</v>
+        <v>550855</v>
       </c>
       <c r="R26" t="n">
-        <v>7244897</v>
+        <v>7245196</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122647126</v>
+        <v>122646847</v>
       </c>
       <c r="B39" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550801</v>
+        <v>550746</v>
       </c>
       <c r="R39" t="n">
-        <v>7244998</v>
+        <v>7244802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646857</v>
+        <v>122646824</v>
       </c>
       <c r="B40" t="n">
-        <v>74868</v>
+        <v>90952</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550751</v>
+        <v>550678</v>
       </c>
       <c r="R40" t="n">
-        <v>7244916</v>
+        <v>7244623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646847</v>
+        <v>122647126</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550746</v>
+        <v>550801</v>
       </c>
       <c r="R41" t="n">
-        <v>7244802</v>
+        <v>7244998</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646824</v>
+        <v>122646857</v>
       </c>
       <c r="B42" t="n">
-        <v>90952</v>
+        <v>74868</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550678</v>
+        <v>550751</v>
       </c>
       <c r="R42" t="n">
-        <v>7244623</v>
+        <v>7244916</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646872</v>
+        <v>122647138</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550828</v>
+        <v>550832</v>
       </c>
       <c r="R11" t="n">
-        <v>7245091</v>
+        <v>7245128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646852</v>
+        <v>122647137</v>
       </c>
       <c r="B12" t="n">
-        <v>91640</v>
+        <v>91301</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550744</v>
+        <v>550827</v>
       </c>
       <c r="R12" t="n">
-        <v>7244856</v>
+        <v>7245136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646850</v>
+        <v>122646871</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550760</v>
+        <v>550784</v>
       </c>
       <c r="R13" t="n">
-        <v>7244829</v>
+        <v>7245041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,11 +1979,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646866</v>
+        <v>122646861</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550706</v>
+        <v>550710</v>
       </c>
       <c r="R14" t="n">
-        <v>7245009</v>
+        <v>7244974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122646808</v>
+        <v>122647146</v>
       </c>
       <c r="B15" t="n">
-        <v>57589</v>
+        <v>57398</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>102110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550651</v>
+        <v>550861</v>
       </c>
       <c r="R15" t="n">
-        <v>7244779</v>
+        <v>7245193</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,12 +2185,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2226,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646878</v>
+        <v>122646869</v>
       </c>
       <c r="B16" t="n">
-        <v>97319</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,25 +2238,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550829</v>
+        <v>550688</v>
       </c>
       <c r="R16" t="n">
-        <v>7245185</v>
+        <v>7245034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646865</v>
+        <v>122646863</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>94778</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2813</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550706</v>
+        <v>550698</v>
       </c>
       <c r="R17" t="n">
-        <v>7245002</v>
+        <v>7244980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646856</v>
+        <v>122646845</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550759</v>
+        <v>550631</v>
       </c>
       <c r="R18" t="n">
-        <v>7244890</v>
+        <v>7244710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646861</v>
+        <v>122646865</v>
       </c>
       <c r="B19" t="n">
-        <v>74847</v>
+        <v>79876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550710</v>
+        <v>550706</v>
       </c>
       <c r="R19" t="n">
-        <v>7244974</v>
+        <v>7245002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647146</v>
+        <v>122646855</v>
       </c>
       <c r="B20" t="n">
-        <v>57398</v>
+        <v>94766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102110</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550861</v>
+        <v>550770</v>
       </c>
       <c r="R20" t="n">
-        <v>7245193</v>
+        <v>7244875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,17 +2720,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,7 +2745,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2761,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646845</v>
+        <v>122646870</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>74858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2777,21 +2772,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550631</v>
+        <v>550726</v>
       </c>
       <c r="R21" t="n">
-        <v>7244710</v>
+        <v>7245050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646863</v>
+        <v>122646824</v>
       </c>
       <c r="B22" t="n">
-        <v>94778</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,25 +2874,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550698</v>
+        <v>550678</v>
       </c>
       <c r="R22" t="n">
-        <v>7244980</v>
+        <v>7244623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122646849</v>
+        <v>122647126</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2989,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3013,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550779</v>
+        <v>550801</v>
       </c>
       <c r="R23" t="n">
-        <v>7244796</v>
+        <v>7244998</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,12 +3038,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,7 +3063,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646853</v>
+        <v>122646857</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550761</v>
+        <v>550751</v>
       </c>
       <c r="R24" t="n">
-        <v>7244876</v>
+        <v>7244916</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646854</v>
+        <v>122646872</v>
       </c>
       <c r="B25" t="n">
-        <v>94766</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550764</v>
+        <v>550828</v>
       </c>
       <c r="R25" t="n">
-        <v>7244897</v>
+        <v>7245091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122647145</v>
+        <v>122646878</v>
       </c>
       <c r="B26" t="n">
-        <v>88303</v>
+        <v>97319</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3303,25 +3298,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550855</v>
+        <v>550829</v>
       </c>
       <c r="R26" t="n">
-        <v>7245196</v>
+        <v>7245185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,12 +3356,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,7 +3381,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3397,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122646869</v>
+        <v>122647145</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>88303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3413,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3437,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550688</v>
+        <v>550855</v>
       </c>
       <c r="R27" t="n">
-        <v>7245034</v>
+        <v>7245196</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,12 +3462,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3492,7 +3487,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3503,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122647144</v>
+        <v>122646854</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>94766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550854</v>
+        <v>550764</v>
       </c>
       <c r="R28" t="n">
-        <v>7245180</v>
+        <v>7244897</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,7 +3593,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3609,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646851</v>
+        <v>122646874</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>74868</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3625,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550748</v>
+        <v>550824</v>
       </c>
       <c r="R29" t="n">
-        <v>7244855</v>
+        <v>7245149</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646855</v>
+        <v>122646850</v>
       </c>
       <c r="B30" t="n">
-        <v>94766</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,21 +3726,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550770</v>
+        <v>550760</v>
       </c>
       <c r="R30" t="n">
-        <v>7244875</v>
+        <v>7244829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,6 +3786,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122647137</v>
+        <v>122646849</v>
       </c>
       <c r="B31" t="n">
-        <v>91301</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550827</v>
+        <v>550779</v>
       </c>
       <c r="R31" t="n">
-        <v>7245136</v>
+        <v>7244796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646873</v>
+        <v>122646851</v>
       </c>
       <c r="B32" t="n">
-        <v>57589</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550828</v>
+        <v>550748</v>
       </c>
       <c r="R32" t="n">
-        <v>7245125</v>
+        <v>7244855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646848</v>
+        <v>122646823</v>
       </c>
       <c r="B33" t="n">
-        <v>91640</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4045,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550776</v>
+        <v>550677</v>
       </c>
       <c r="R33" t="n">
-        <v>7244797</v>
+        <v>7244586</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646822</v>
+        <v>122646848</v>
       </c>
       <c r="B34" t="n">
-        <v>96233</v>
+        <v>91640</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1841</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550659</v>
+        <v>550776</v>
       </c>
       <c r="R34" t="n">
-        <v>7244555</v>
+        <v>7244797</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646846</v>
+        <v>122646856</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550720</v>
+        <v>550759</v>
       </c>
       <c r="R35" t="n">
-        <v>7244779</v>
+        <v>7244890</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646864</v>
+        <v>122646846</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4367,21 +4367,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550696</v>
+        <v>550720</v>
       </c>
       <c r="R36" t="n">
-        <v>7244978</v>
+        <v>7244779</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646870</v>
+        <v>122646864</v>
       </c>
       <c r="B37" t="n">
-        <v>74858</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,21 +4473,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550726</v>
+        <v>550696</v>
       </c>
       <c r="R37" t="n">
-        <v>7245050</v>
+        <v>7244978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646874</v>
+        <v>122646821</v>
       </c>
       <c r="B38" t="n">
-        <v>74868</v>
+        <v>74858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,21 +4579,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550824</v>
+        <v>550670</v>
       </c>
       <c r="R38" t="n">
-        <v>7245149</v>
+        <v>7244542</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122646847</v>
+        <v>122647136</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550746</v>
+        <v>550831</v>
       </c>
       <c r="R39" t="n">
-        <v>7244802</v>
+        <v>7245134</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646824</v>
+        <v>122646808</v>
       </c>
       <c r="B40" t="n">
-        <v>90952</v>
+        <v>57589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4787,25 +4787,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550678</v>
+        <v>550651</v>
       </c>
       <c r="R40" t="n">
-        <v>7244623</v>
+        <v>7244779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122647126</v>
+        <v>122646866</v>
       </c>
       <c r="B41" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550801</v>
+        <v>550706</v>
       </c>
       <c r="R41" t="n">
-        <v>7244998</v>
+        <v>7245009</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122646857</v>
+        <v>122647144</v>
       </c>
       <c r="B42" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550751</v>
+        <v>550854</v>
       </c>
       <c r="R42" t="n">
-        <v>7244916</v>
+        <v>7245180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122647136</v>
+        <v>122646868</v>
       </c>
       <c r="B43" t="n">
-        <v>91243</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550831</v>
+        <v>550694</v>
       </c>
       <c r="R43" t="n">
-        <v>7245134</v>
+        <v>7245016</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5199,7 +5199,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646823</v>
+        <v>122646853</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550677</v>
+        <v>550761</v>
       </c>
       <c r="R44" t="n">
-        <v>7244586</v>
+        <v>7244876</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646868</v>
+        <v>122646873</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550694</v>
+        <v>550828</v>
       </c>
       <c r="R45" t="n">
-        <v>7245016</v>
+        <v>7245125</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646821</v>
+        <v>122646822</v>
       </c>
       <c r="B46" t="n">
-        <v>74858</v>
+        <v>96233</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>310</v>
+        <v>1841</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550670</v>
+        <v>550659</v>
       </c>
       <c r="R46" t="n">
-        <v>7244542</v>
+        <v>7244555</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122647138</v>
+        <v>122646852</v>
       </c>
       <c r="B47" t="n">
-        <v>90952</v>
+        <v>91640</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550832</v>
+        <v>550744</v>
       </c>
       <c r="R47" t="n">
-        <v>7245128</v>
+        <v>7244856</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,7 +5623,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646871</v>
+        <v>122646847</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550784</v>
+        <v>550746</v>
       </c>
       <c r="R48" t="n">
-        <v>7245041</v>
+        <v>7244802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -2226,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646869</v>
+        <v>122646845</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550688</v>
+        <v>550631</v>
       </c>
       <c r="R16" t="n">
-        <v>7245034</v>
+        <v>7244710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646863</v>
+        <v>122646869</v>
       </c>
       <c r="B17" t="n">
-        <v>94778</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2813</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550698</v>
+        <v>550688</v>
       </c>
       <c r="R17" t="n">
-        <v>7244980</v>
+        <v>7245034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646845</v>
+        <v>122646863</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>94778</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550631</v>
+        <v>550698</v>
       </c>
       <c r="R18" t="n">
-        <v>7244710</v>
+        <v>7244980</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646857</v>
+        <v>122646878</v>
       </c>
       <c r="B24" t="n">
-        <v>74868</v>
+        <v>97319</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550751</v>
+        <v>550829</v>
       </c>
       <c r="R24" t="n">
-        <v>7244916</v>
+        <v>7245185</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646872</v>
+        <v>122646857</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>74868</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550828</v>
+        <v>550751</v>
       </c>
       <c r="R25" t="n">
-        <v>7245091</v>
+        <v>7244916</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646878</v>
+        <v>122646872</v>
       </c>
       <c r="B26" t="n">
-        <v>97319</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,25 +3298,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550829</v>
+        <v>550828</v>
       </c>
       <c r="R26" t="n">
-        <v>7245185</v>
+        <v>7245091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646848</v>
+        <v>122646856</v>
       </c>
       <c r="B34" t="n">
-        <v>91640</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,25 +4151,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550776</v>
+        <v>550759</v>
       </c>
       <c r="R34" t="n">
-        <v>7244797</v>
+        <v>7244890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122646856</v>
+        <v>122646848</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550759</v>
+        <v>550776</v>
       </c>
       <c r="R35" t="n">
-        <v>7244890</v>
+        <v>7244797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646868</v>
+        <v>122646873</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,25 +5105,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550694</v>
+        <v>550828</v>
       </c>
       <c r="R43" t="n">
-        <v>7245016</v>
+        <v>7245125</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646853</v>
+        <v>122646868</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550761</v>
+        <v>550694</v>
       </c>
       <c r="R44" t="n">
-        <v>7244876</v>
+        <v>7245016</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646873</v>
+        <v>122646853</v>
       </c>
       <c r="B45" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550828</v>
+        <v>550761</v>
       </c>
       <c r="R45" t="n">
-        <v>7245125</v>
+        <v>7244876</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646878</v>
+        <v>122646857</v>
       </c>
       <c r="B24" t="n">
-        <v>97319</v>
+        <v>74868</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550829</v>
+        <v>550751</v>
       </c>
       <c r="R24" t="n">
-        <v>7245185</v>
+        <v>7244916</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646857</v>
+        <v>122646872</v>
       </c>
       <c r="B25" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550751</v>
+        <v>550828</v>
       </c>
       <c r="R25" t="n">
-        <v>7244916</v>
+        <v>7245091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646872</v>
+        <v>122646878</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>97319</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,25 +3298,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550828</v>
+        <v>550829</v>
       </c>
       <c r="R26" t="n">
-        <v>7245091</v>
+        <v>7245185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646851</v>
+        <v>122646823</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,21 +3943,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550748</v>
+        <v>550677</v>
       </c>
       <c r="R32" t="n">
-        <v>7244855</v>
+        <v>7244586</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646823</v>
+        <v>122646851</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550677</v>
+        <v>550748</v>
       </c>
       <c r="R33" t="n">
-        <v>7244586</v>
+        <v>7244855</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646822</v>
+        <v>122646852</v>
       </c>
       <c r="B46" t="n">
-        <v>96233</v>
+        <v>91640</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1841</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550659</v>
+        <v>550744</v>
       </c>
       <c r="R46" t="n">
-        <v>7244555</v>
+        <v>7244856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646852</v>
+        <v>122646822</v>
       </c>
       <c r="B47" t="n">
-        <v>91640</v>
+        <v>96233</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>1841</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550744</v>
+        <v>550659</v>
       </c>
       <c r="R47" t="n">
-        <v>7244856</v>
+        <v>7244555</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647138</v>
+        <v>122646871</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550832</v>
+        <v>550784</v>
       </c>
       <c r="R11" t="n">
-        <v>7245128</v>
+        <v>7245041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647137</v>
+        <v>122646851</v>
       </c>
       <c r="B12" t="n">
-        <v>91301</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550827</v>
+        <v>550748</v>
       </c>
       <c r="R12" t="n">
-        <v>7245136</v>
+        <v>7244855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646871</v>
+        <v>122646823</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550784</v>
+        <v>550677</v>
       </c>
       <c r="R13" t="n">
-        <v>7245041</v>
+        <v>7244586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122646861</v>
+        <v>122647126</v>
       </c>
       <c r="B14" t="n">
-        <v>74847</v>
+        <v>91243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,25 +2021,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550710</v>
+        <v>550801</v>
       </c>
       <c r="R14" t="n">
-        <v>7244974</v>
+        <v>7244998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647146</v>
+        <v>122646850</v>
       </c>
       <c r="B15" t="n">
-        <v>57398</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102110</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550861</v>
+        <v>550760</v>
       </c>
       <c r="R15" t="n">
-        <v>7245193</v>
+        <v>7244829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,17 +2185,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Kom lågt överskotten, varnade flög mot SV</t>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2226,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122646845</v>
+        <v>122646873</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,25 +2238,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550631</v>
+        <v>550828</v>
       </c>
       <c r="R16" t="n">
-        <v>7244710</v>
+        <v>7245125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122646869</v>
+        <v>122647145</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>88303</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550688</v>
+        <v>550855</v>
       </c>
       <c r="R17" t="n">
-        <v>7245034</v>
+        <v>7245196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122646863</v>
+        <v>122646854</v>
       </c>
       <c r="B18" t="n">
-        <v>94778</v>
+        <v>94766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550698</v>
+        <v>550764</v>
       </c>
       <c r="R18" t="n">
-        <v>7244980</v>
+        <v>7244897</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122646865</v>
+        <v>122646846</v>
       </c>
       <c r="B19" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2556,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550706</v>
+        <v>550720</v>
       </c>
       <c r="R19" t="n">
-        <v>7245002</v>
+        <v>7244779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122646855</v>
+        <v>122646865</v>
       </c>
       <c r="B20" t="n">
-        <v>94766</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550770</v>
+        <v>550706</v>
       </c>
       <c r="R20" t="n">
-        <v>7244875</v>
+        <v>7245002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122646870</v>
+        <v>122647138</v>
       </c>
       <c r="B21" t="n">
-        <v>74858</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550726</v>
+        <v>550832</v>
       </c>
       <c r="R21" t="n">
-        <v>7245050</v>
+        <v>7245128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122646824</v>
+        <v>122646822</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>96233</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1841</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550678</v>
+        <v>550659</v>
       </c>
       <c r="R22" t="n">
-        <v>7244623</v>
+        <v>7244555</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122647126</v>
+        <v>122646857</v>
       </c>
       <c r="B23" t="n">
-        <v>91243</v>
+        <v>74868</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,21 +2984,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550801</v>
+        <v>550751</v>
       </c>
       <c r="R23" t="n">
-        <v>7244998</v>
+        <v>7244916</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122646857</v>
+        <v>122646856</v>
       </c>
       <c r="B24" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550751</v>
+        <v>550759</v>
       </c>
       <c r="R24" t="n">
-        <v>7244916</v>
+        <v>7244890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122646872</v>
+        <v>122646869</v>
       </c>
       <c r="B25" t="n">
         <v>74863</v>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550828</v>
+        <v>550688</v>
       </c>
       <c r="R25" t="n">
-        <v>7245091</v>
+        <v>7245034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122646878</v>
+        <v>122646821</v>
       </c>
       <c r="B26" t="n">
-        <v>97319</v>
+        <v>74858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,25 +3298,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550829</v>
+        <v>550670</v>
       </c>
       <c r="R26" t="n">
-        <v>7245185</v>
+        <v>7244542</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122647145</v>
+        <v>122646863</v>
       </c>
       <c r="B27" t="n">
-        <v>88303</v>
+        <v>94778</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>2813</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550855</v>
+        <v>550698</v>
       </c>
       <c r="R27" t="n">
-        <v>7245196</v>
+        <v>7244980</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122646854</v>
+        <v>122647137</v>
       </c>
       <c r="B28" t="n">
-        <v>94766</v>
+        <v>91301</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550764</v>
+        <v>550827</v>
       </c>
       <c r="R28" t="n">
-        <v>7244897</v>
+        <v>7245136</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122646874</v>
+        <v>122647144</v>
       </c>
       <c r="B29" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550824</v>
+        <v>550854</v>
       </c>
       <c r="R29" t="n">
-        <v>7245149</v>
+        <v>7245180</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122646850</v>
+        <v>122646824</v>
       </c>
       <c r="B30" t="n">
-        <v>56688</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550760</v>
+        <v>550678</v>
       </c>
       <c r="R30" t="n">
-        <v>7244829</v>
+        <v>7244623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,11 +3786,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122646849</v>
+        <v>122646878</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>97319</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,25 +3828,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550779</v>
+        <v>550829</v>
       </c>
       <c r="R31" t="n">
-        <v>7244796</v>
+        <v>7245185</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122646823</v>
+        <v>122646808</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3934,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550677</v>
+        <v>550651</v>
       </c>
       <c r="R32" t="n">
-        <v>7244586</v>
+        <v>7244779</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4033,10 +4028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122646851</v>
+        <v>122646855</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>94766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,25 +4040,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550748</v>
+        <v>550770</v>
       </c>
       <c r="R33" t="n">
-        <v>7244855</v>
+        <v>7244875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122646856</v>
+        <v>122646872</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4155,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550759</v>
+        <v>550828</v>
       </c>
       <c r="R34" t="n">
-        <v>7244890</v>
+        <v>7245091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4351,7 +4346,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122646846</v>
+        <v>122646868</v>
       </c>
       <c r="B36" t="n">
         <v>74863</v>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550720</v>
+        <v>550694</v>
       </c>
       <c r="R36" t="n">
-        <v>7244779</v>
+        <v>7245016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122646864</v>
+        <v>122646870</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>74858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,21 +4468,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550696</v>
+        <v>550726</v>
       </c>
       <c r="R37" t="n">
-        <v>7244978</v>
+        <v>7245050</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122646821</v>
+        <v>122646866</v>
       </c>
       <c r="B38" t="n">
-        <v>74858</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,21 +4574,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4603,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550670</v>
+        <v>550706</v>
       </c>
       <c r="R38" t="n">
-        <v>7244542</v>
+        <v>7245009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122647136</v>
+        <v>122646861</v>
       </c>
       <c r="B39" t="n">
-        <v>91243</v>
+        <v>74847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,25 +4676,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4709,10 +4704,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550831</v>
+        <v>550710</v>
       </c>
       <c r="R39" t="n">
-        <v>7245134</v>
+        <v>7244974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4739,12 +4734,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4759,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4775,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122646808</v>
+        <v>122646853</v>
       </c>
       <c r="B40" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550651</v>
+        <v>550761</v>
       </c>
       <c r="R40" t="n">
-        <v>7244779</v>
+        <v>7244876</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,7 +4876,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122646866</v>
+        <v>122646845</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4921,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550706</v>
+        <v>550631</v>
       </c>
       <c r="R41" t="n">
-        <v>7245009</v>
+        <v>7244710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,7 +4982,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122647144</v>
+        <v>122646847</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550854</v>
+        <v>550746</v>
       </c>
       <c r="R42" t="n">
-        <v>7245180</v>
+        <v>7244802</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,12 +5052,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5082,7 +5077,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5093,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122646873</v>
+        <v>122647136</v>
       </c>
       <c r="B43" t="n">
-        <v>57589</v>
+        <v>91243</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,25 +5100,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550828</v>
+        <v>550831</v>
       </c>
       <c r="R43" t="n">
-        <v>7245125</v>
+        <v>7245134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,12 +5158,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5183,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5199,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122646868</v>
+        <v>122646874</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>74868</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5210,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550694</v>
+        <v>550824</v>
       </c>
       <c r="R44" t="n">
-        <v>7245016</v>
+        <v>7245149</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122646853</v>
+        <v>122647146</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57398</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5321,21 +5316,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>102110</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5345,10 +5340,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550761</v>
+        <v>550861</v>
       </c>
       <c r="R45" t="n">
-        <v>7244876</v>
+        <v>7245193</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,12 +5370,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kom lågt överskotten, varnade flög mot SV</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122646852</v>
+        <v>122646849</v>
       </c>
       <c r="B46" t="n">
-        <v>91640</v>
+        <v>90952</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550744</v>
+        <v>550779</v>
       </c>
       <c r="R46" t="n">
-        <v>7244856</v>
+        <v>7244796</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122646822</v>
+        <v>122646864</v>
       </c>
       <c r="B47" t="n">
-        <v>96233</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550659</v>
+        <v>550696</v>
       </c>
       <c r="R47" t="n">
-        <v>7244555</v>
+        <v>7244978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122646847</v>
+        <v>122646852</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,25 +5635,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550746</v>
+        <v>550744</v>
       </c>
       <c r="R48" t="n">
-        <v>7244802</v>
+        <v>7244856</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 12330-2023 artfynd.xlsx
+++ b/artfynd/A 12330-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88130186</v>
+        <v>88130188</v>
       </c>
       <c r="B2" t="n">
-        <v>76968</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1561</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Urnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tholurna dissimilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) Norman</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552097.9252604182</v>
+        <v>552100</v>
       </c>
       <c r="R2" t="n">
-        <v>7244095.954430577</v>
+        <v>7244131</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88130193</v>
+        <v>88130187</v>
       </c>
       <c r="B3" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vaartoe, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552074.8751319676</v>
+        <v>552100</v>
       </c>
       <c r="R3" t="n">
-        <v>7244049.961810584</v>
+        <v>7244131</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,28 +840,17 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88130185</v>
+        <v>88130191</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552035.1449950821</v>
+        <v>552135</v>
       </c>
       <c r="R4" t="n">
-        <v>7244071.004447591</v>
+        <v>7244112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,19 +937,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88130191</v>
+        <v>88130193</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vaartoe, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552134.9024572875</v>
+        <v>552075</v>
       </c>
       <c r="R5" t="n">
-        <v>7244112.083670973</v>
+        <v>7244050</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,27 +1037,18 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88130187</v>
+        <v>88130186</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1561</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Urnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tholurna dissimilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) Norman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552099.813855423</v>
+        <v>552098</v>
       </c>
       <c r="R6" t="n">
-        <v>7244131.116378064</v>
+        <v>7244096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,19 +1135,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1167,7 @@
         <v>88130184</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552035.1449950821</v>
+        <v>552035</v>
       </c>
       <c r="R7" t="n">
-        <v>7244071.004447591</v>
+        <v>7244071</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,19 +1232,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,50 +1261,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88130190</v>
+        <v>88130189</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vaartoe, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552127.1639213613</v>
+        <v>552142</v>
       </c>
       <c r="R8" t="n">
-        <v>7244147.074637947</v>
+        <v>7244164</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,27 +1332,18 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,37 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88130188</v>
+        <v>88130190</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552099.813855423</v>
+        <v>552127</v>
       </c>
       <c r="R9" t="n">
-        <v>7244131.116378064</v>
+        <v>7244147</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1536,19 +1430,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1459,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88130189</v>
+        <v>88130185</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vaartoe, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552141.9349698082</v>
+        <v>552035</v>
       </c>
       <c r="R10" t="n">
-        <v>7244164.064364077</v>
+        <v>7244071</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1651,28 +1527,17 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
